--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/luis_fuentes_virtualsoft_tech/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9974B-1081-44A4-BE8C-281FC6BCBC91}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{94C845A1-4725-47C1-B6E7-67D7B6C838DB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{6FAB5C00-0D52-4A17-B156-712996171C9E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
     <sheet name="Semana 2 - 7 Sep al 13 Sep" sheetId="9" r:id="rId2"/>
     <sheet name="Semana 3 - 14 al 20 Sep" sheetId="15" r:id="rId3"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
+    <sheet name="Semana 4 - 21 Sep al 04 Oct" sheetId="16" r:id="rId4"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="105">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -398,12 +399,42 @@
       <t>lunes y Martes hasta 1:00pm y Miercoles y Jueves hasta las 11:00am, en ausencia de Josue</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>Apoyo Revisión GGR negativo casino / deportivo//</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Martes y Jueves en ausencia de Juan Jose</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Apoyo Deltas (Registros, Bonos, Premios Bonos y Bonos Casino)//</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Martes y Jueves en ausencia de Juan Jose</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,6 +505,17 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -613,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -677,15 +719,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -708,6 +741,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -720,8 +771,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -729,7 +780,377 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="67">
+  <dxfs count="104">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1749,23 +2170,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" s="2" customFormat="1">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="34"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="23"/>
-      <c r="H2" s="23" t="s">
+      <c r="F2" s="34"/>
+      <c r="H2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="23"/>
-      <c r="K2" s="23" t="s">
+      <c r="I2" s="34"/>
+      <c r="K2" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="23"/>
+      <c r="L2" s="34"/>
     </row>
     <row r="3" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B3" s="3" t="s">
@@ -2120,14 +2541,14 @@
       </c>
     </row>
     <row r="17" spans="2:12" s="2" customFormat="1">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="E17" s="23" t="s">
+      <c r="C17" s="34"/>
+      <c r="E17" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="23"/>
+      <c r="F17" s="34"/>
     </row>
     <row r="18" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B18" s="3" t="s">
@@ -2142,14 +2563,14 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="23"/>
-      <c r="K18" s="23" t="s">
+      <c r="I18" s="34"/>
+      <c r="K18" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="23"/>
+      <c r="L18" s="34"/>
     </row>
     <row r="19" spans="2:12" s="2" customFormat="1" ht="28.95" customHeight="1">
       <c r="B19" s="6" t="s">
@@ -2435,14 +2856,14 @@
       </c>
       <c r="D32"/>
       <c r="F32" s="1"/>
-      <c r="H32" s="24" t="s">
+      <c r="H32" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="25"/>
-      <c r="K32" s="23" t="s">
+      <c r="I32" s="36"/>
+      <c r="K32" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="23"/>
+      <c r="L32" s="34"/>
     </row>
     <row r="33" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B33" s="6" t="s">
@@ -2600,118 +3021,118 @@
     <mergeCell ref="E17:F17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="66" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="65" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="64" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="63" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B31">
-    <cfRule type="duplicateValues" dxfId="62" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="61" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B34 B9">
-    <cfRule type="duplicateValues" dxfId="60" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B29 B11">
-    <cfRule type="duplicateValues" dxfId="59" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="58" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="57" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="56" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="55" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="54" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="53" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="52" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="51" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="duplicateValues" dxfId="50" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="49" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="47" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="46" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="45" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H26">
-    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="duplicateValues" dxfId="41" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="40" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="39" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="38" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="37" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="36" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="35" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="34" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="33" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="32" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="duplicateValues" dxfId="31" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="duplicateValues" dxfId="30" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="duplicateValues" dxfId="29" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="23"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2749,25 +3170,25 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2"/>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="34"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="23"/>
+      <c r="F2" s="34"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="23"/>
+      <c r="I2" s="34"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="23"/>
+      <c r="L2" s="34"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="2"/>
@@ -3183,10 +3604,10 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2"/>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="23"/>
+      <c r="C17" s="34"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="G17" s="2"/>
@@ -3205,20 +3626,20 @@
         <v>5</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="23"/>
+      <c r="F18" s="34"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="23"/>
+      <c r="I18" s="34"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="23" t="s">
+      <c r="K18" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="23"/>
+      <c r="L18" s="34"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="2"/>
@@ -3446,10 +3867,10 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2"/>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="23"/>
+      <c r="C27" s="34"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="1"/>
@@ -3575,15 +3996,15 @@
       <c r="E32" s="2"/>
       <c r="F32" s="1"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="24" t="s">
+      <c r="H32" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="25"/>
+      <c r="I32" s="36"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="23" t="s">
+      <c r="K32" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="23"/>
+      <c r="L32" s="34"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="2"/>
@@ -3738,91 +4159,91 @@
     <mergeCell ref="K18:L18"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12 B15">
-    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B31">
-    <cfRule type="duplicateValues" dxfId="24" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34 B29 B11">
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23">
-    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K26">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3848,64 +4269,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="34"/>
-      <c r="B1" s="34"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="26"/>
+      <c r="A1" s="37"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="23"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="26"/>
-      <c r="B2" s="35" t="s">
+      <c r="A2" s="23"/>
+      <c r="B2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="35" t="s">
+      <c r="C2" s="39"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="36"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="35" t="s">
+      <c r="F2" s="39"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="36"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="35" t="s">
+      <c r="I2" s="39"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="36"/>
+      <c r="L2" s="39"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
-      <c r="A3" s="26"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="27"/>
+      <c r="D3" s="24"/>
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="26"/>
+      <c r="G3" s="23"/>
       <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="26"/>
+      <c r="J3" s="23"/>
       <c r="K3" s="3" t="s">
         <v>4</v>
       </c>
@@ -3914,450 +4335,450 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="14.4">
-      <c r="A4" s="26"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="26"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="26"/>
+      <c r="J4" s="23"/>
       <c r="K4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="14.4">
-      <c r="A5" s="26"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="26"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="23"/>
       <c r="H5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="26"/>
+      <c r="J5" s="23"/>
       <c r="K5" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="L5" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="14.4">
-      <c r="A6" s="26"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="26"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="23"/>
       <c r="H6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="26"/>
+      <c r="J6" s="23"/>
       <c r="K6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="29" t="s">
+      <c r="L6" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="14.4">
-      <c r="A7" s="26"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="26"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="23"/>
       <c r="H7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="23"/>
       <c r="K7" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="14.4">
-      <c r="A8" s="26"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="26"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="23"/>
       <c r="H8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="I8" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="26"/>
+      <c r="J8" s="23"/>
       <c r="K8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="29" t="s">
+      <c r="L8" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="14.4">
-      <c r="A9" s="26"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="26"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="26"/>
+      <c r="G9" s="23"/>
       <c r="H9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="23"/>
       <c r="K9" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="L9" s="29" t="s">
+      <c r="L9" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="14.4">
-      <c r="A10" s="26"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="26"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="23"/>
       <c r="H10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="I10" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="26"/>
+      <c r="J10" s="23"/>
       <c r="K10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="29" t="s">
+      <c r="L10" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="14.4">
-      <c r="A11" s="26"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="26"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="23"/>
       <c r="H11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="29" t="s">
+      <c r="I11" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="23"/>
       <c r="K11" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="29" t="s">
+      <c r="L11" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="14.4">
-      <c r="A12" s="26"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="26"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="23"/>
       <c r="H12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="26"/>
+      <c r="J12" s="23"/>
       <c r="K12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="29" t="s">
+      <c r="L12" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="41.4">
-      <c r="A13" s="26"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="27"/>
+      <c r="D13" s="24"/>
       <c r="E13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="23"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="29" t="s">
+      <c r="I13" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J13" s="26"/>
+      <c r="J13" s="23"/>
       <c r="K13" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="L13" s="29" t="s">
+      <c r="L13" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="41.4">
-      <c r="A14" s="26"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="27"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J14" s="26"/>
+      <c r="J14" s="23"/>
       <c r="K14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L14" s="29" t="s">
+      <c r="L14" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="14.4">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="26"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="26"/>
+      <c r="G15" s="23"/>
       <c r="H15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="29" t="s">
+      <c r="I15" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="26"/>
+      <c r="J15" s="23"/>
       <c r="K15" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="L15" s="29" t="s">
+      <c r="L15" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="14.4">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J16" s="27"/>
+      <c r="J16" s="24"/>
       <c r="K16" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="L16" s="29" t="s">
+      <c r="L16" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="26"/>
-      <c r="B17" s="35" t="s">
+      <c r="A17" s="23"/>
+      <c r="B17" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="35" t="s">
+      <c r="C17" s="39"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="36"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="26"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="23"/>
     </row>
     <row r="18" spans="1:12" ht="14.4">
-      <c r="A18" s="26"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="26"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="26"/>
-      <c r="H18" s="35" t="s">
+      <c r="G18" s="23"/>
+      <c r="H18" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="36"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="35" t="s">
+      <c r="I18" s="39"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="36"/>
+      <c r="L18" s="39"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
-      <c r="A19" s="26"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="26"/>
+      <c r="D19" s="23"/>
       <c r="E19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="26"/>
+      <c r="G19" s="23"/>
       <c r="H19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J19" s="26"/>
+      <c r="J19" s="23"/>
       <c r="K19" s="3" t="s">
         <v>6</v>
       </c>
@@ -4366,356 +4787,356 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="14.4">
-      <c r="A20" s="26"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="26"/>
+      <c r="D20" s="23"/>
       <c r="E20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="26"/>
+      <c r="G20" s="23"/>
       <c r="H20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I20" s="29" t="s">
+      <c r="I20" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="26"/>
-      <c r="K20" s="30" t="s">
+      <c r="J20" s="23"/>
+      <c r="K20" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="L20" s="28" t="s">
+      <c r="L20" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="26"/>
+      <c r="A21" s="23"/>
       <c r="B21" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="26"/>
+      <c r="D21" s="23"/>
       <c r="E21" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="26"/>
+      <c r="G21" s="23"/>
       <c r="H21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="28" t="s">
+      <c r="I21" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="26"/>
-      <c r="K21" s="30" t="s">
+      <c r="J21" s="23"/>
+      <c r="K21" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="L21" s="28" t="s">
+      <c r="L21" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="14.4">
-      <c r="A22" s="26"/>
+      <c r="A22" s="23"/>
       <c r="B22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="26"/>
+      <c r="D22" s="23"/>
       <c r="E22" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G22" s="26"/>
+      <c r="G22" s="23"/>
       <c r="H22" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I22" s="29" t="s">
+      <c r="I22" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="26"/>
-      <c r="K22" s="30" t="s">
+      <c r="J22" s="23"/>
+      <c r="K22" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="L22" s="28" t="s">
+      <c r="L22" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="26"/>
+      <c r="A23" s="23"/>
       <c r="B23" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="26"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="23"/>
       <c r="H23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I23" s="28" t="s">
+      <c r="I23" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="26"/>
-      <c r="K23" s="30" t="s">
+      <c r="J23" s="23"/>
+      <c r="K23" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="28" t="s">
+      <c r="L23" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="41.4">
-      <c r="A24" s="26"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="26"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="23"/>
       <c r="H24" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="29" t="s">
+      <c r="I24" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="26"/>
-      <c r="K24" s="30" t="s">
+      <c r="J24" s="23"/>
+      <c r="K24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="28" t="s">
+      <c r="L24" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="26"/>
+      <c r="A25" s="23"/>
       <c r="B25" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="26"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="23"/>
       <c r="H25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="I25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J25" s="26"/>
-      <c r="K25" s="30" t="s">
+      <c r="J25" s="23"/>
+      <c r="K25" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="L25" s="28" t="s">
+      <c r="L25" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="14.4">
-      <c r="A26" s="34"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="26"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="23"/>
       <c r="H26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="29" t="s">
+      <c r="I26" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="26"/>
-      <c r="K26" s="30" t="s">
+      <c r="J26" s="23"/>
+      <c r="K26" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="L26" s="28" t="s">
+      <c r="L26" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="26"/>
-      <c r="B27" s="35" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="36"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="26"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="23"/>
       <c r="H27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="28" t="s">
+      <c r="I27" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J27" s="26"/>
-      <c r="K27" s="30" t="s">
+      <c r="J27" s="23"/>
+      <c r="K27" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="L27" s="28" t="s">
+      <c r="L27" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="14.4">
-      <c r="A28" s="26"/>
+      <c r="A28" s="23"/>
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="37"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="26"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="23"/>
       <c r="H28" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="29" t="s">
+      <c r="I28" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="26"/>
-      <c r="K28" s="30" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="L28" s="28" t="s">
+      <c r="L28" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="26"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="37"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="26"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="23"/>
       <c r="H29" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="I29" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="26"/>
-      <c r="K29" s="30" t="s">
+      <c r="J29" s="23"/>
+      <c r="K29" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="L29" s="28" t="s">
+      <c r="L29" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="27.6">
-      <c r="A30" s="26"/>
-      <c r="B30" s="31" t="s">
+      <c r="A30" s="23"/>
+      <c r="B30" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="37"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="26"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="23"/>
       <c r="H30" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="I30" s="29" t="s">
+      <c r="I30" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="27"/>
+      <c r="J30" s="24"/>
       <c r="K30" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="L30" s="28" t="s">
+      <c r="L30" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="26"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="37"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="26"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="26"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="35" t="s">
+      <c r="D32" s="41"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="40"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="35" t="s">
+      <c r="I32" s="43"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="36"/>
+      <c r="L32" s="39"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
-      <c r="A33" s="26"/>
-      <c r="B33" s="32" t="s">
+      <c r="A33" s="23"/>
+      <c r="B33" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="26"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="23"/>
       <c r="H33" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J33" s="26"/>
+      <c r="J33" s="23"/>
       <c r="K33" s="3" t="s">
         <v>39</v>
       </c>
@@ -4724,172 +5145,172 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="26"/>
-      <c r="B34" s="32" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="26"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="23"/>
       <c r="H34" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="I34" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="26"/>
+      <c r="J34" s="23"/>
       <c r="K34" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="L34" s="28" t="s">
+      <c r="L34" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="26"/>
+      <c r="A35" s="23"/>
       <c r="B35" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="26"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="23"/>
       <c r="H35" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I35" s="28" t="s">
+      <c r="I35" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J35" s="26"/>
+      <c r="J35" s="23"/>
       <c r="K35" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L35" s="28" t="s">
+      <c r="L35" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="26"/>
-      <c r="B36" s="33" t="s">
+      <c r="A36" s="23"/>
+      <c r="B36" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="26"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="23"/>
       <c r="H36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I36" s="28" t="s">
+      <c r="I36" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J36" s="26"/>
+      <c r="J36" s="23"/>
       <c r="K36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L36" s="28" t="s">
+      <c r="L36" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="26"/>
+      <c r="A37" s="23"/>
       <c r="B37" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="26"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="23"/>
       <c r="H37" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="28" t="s">
+      <c r="I37" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J37" s="26"/>
+      <c r="J37" s="23"/>
       <c r="K37" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L37" s="28" t="s">
+      <c r="L37" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="34"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="26"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="23"/>
       <c r="H38" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I38" s="28" t="s">
+      <c r="I38" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J38" s="26"/>
+      <c r="J38" s="23"/>
       <c r="K38" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L38" s="28" t="s">
+      <c r="L38" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="34"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="26"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="37"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="37"/>
+      <c r="K39" s="37"/>
+      <c r="L39" s="23"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="34"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="26"/>
+      <c r="A40" s="37"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="37"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="37"/>
+      <c r="K40" s="37"/>
+      <c r="L40" s="23"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="34"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="26"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="52">
@@ -4905,16 +5326,16 @@
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="J40:K40"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="D37:E37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
     <mergeCell ref="J31:K31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="H32:I32"/>
@@ -4930,13 +5351,13 @@
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G17:H17"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
@@ -4951,6 +5372,964 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42A8CB2C-D9C5-4429-9B06-5F24BAC192A6}">
+  <dimension ref="B2:L39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="3.3984375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="93.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.59765625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="52.59765625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.796875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.59765625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="55" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.59765625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12">
+      <c r="B2" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="34"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="34"/>
+      <c r="H2" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="34"/>
+      <c r="K2" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="34"/>
+    </row>
+    <row r="3" spans="2:12" ht="14.4">
+      <c r="B3" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="14.4">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="14.4">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="14.4">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="14.4">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="14.4">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="14.4">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="14.4">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="14.4">
+      <c r="B11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="14.4">
+      <c r="B12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="14.4">
+      <c r="B13" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="14.4">
+      <c r="B14" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="14.4">
+      <c r="E15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="14.4">
+      <c r="E16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="34"/>
+    </row>
+    <row r="18" spans="2:12" ht="14.4">
+      <c r="B18" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="H18" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="34"/>
+      <c r="K18" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="L18" s="34"/>
+    </row>
+    <row r="19" spans="2:12" ht="14.4">
+      <c r="B19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="34"/>
+      <c r="H19" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="L19" s="33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="14.4">
+      <c r="B20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="14.4">
+      <c r="B21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="14.4">
+      <c r="B22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="14.4">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="27.6">
+      <c r="B24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="14.4">
+      <c r="B25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="14.4">
+      <c r="H26" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="14.4">
+      <c r="B27" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="34"/>
+      <c r="H27" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="14.4">
+      <c r="B28" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="14.4">
+      <c r="B29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" ht="14.4">
+      <c r="B30" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I30" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12">
+      <c r="B31" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12">
+      <c r="B32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32"/>
+      <c r="H32" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="I32" s="36"/>
+      <c r="K32" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="L32" s="34"/>
+    </row>
+    <row r="33" spans="2:12" ht="14.4">
+      <c r="B33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33"/>
+      <c r="H33" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="L33" s="31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34"/>
+      <c r="H34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35"/>
+      <c r="H35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36"/>
+      <c r="H36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="D37"/>
+      <c r="H37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12">
+      <c r="D38"/>
+      <c r="H38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="D39"/>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="d7vKTB1NsKMzTP3OJzvu/ePVtZYm0laOc19cvVp4GYSG6Ps8to4DQt2UeZgMqFeJ7HXLpxvodTZ7LAlW0JWT+Q==" saltValue="KW8KYlaKpYzqhnMAW6lRXg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="11">
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="35" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="34" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9 B33:B34">
+    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12 B15">
+    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25 B31">
+    <cfRule type="duplicateValues" dxfId="31" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32 B10">
+    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35 B29 B11">
+    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="28" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="25" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15 E17">
+    <cfRule type="duplicateValues" dxfId="21" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24">
+    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H24">
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25:H26">
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H30">
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37">
+    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H38">
+    <cfRule type="duplicateValues" dxfId="10" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4">
+    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11">
+    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12">
+    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13">
+    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K16">
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K24">
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K25:K26">
+    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K30">
+    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37">
+    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K38">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="95.19921875" defaultRowHeight="13.8"/>
@@ -5166,6 +6545,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -5366,22 +6754,21 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5400,19 +6787,11 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/luis_fuentes_virtualsoft_tech/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{94C845A1-4725-47C1-B6E7-67D7B6C838DB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{6FAB5C00-0D52-4A17-B156-712996171C9E}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{94C845A1-4725-47C1-B6E7-67D7B6C838DB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{B4F5BB62-2075-44F6-80BA-4B8BF413BC82}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
     <sheet name="Semana 2 - 7 Sep al 13 Sep" sheetId="9" r:id="rId2"/>
     <sheet name="Semana 3 - 14 al 20 Sep" sheetId="15" r:id="rId3"/>
-    <sheet name="Semana 4 - 21 Sep al 04 Oct" sheetId="16" r:id="rId4"/>
+    <sheet name="Semana 4 - 21 Sep al 04 Oct" sheetId="17" r:id="rId4"/>
     <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="106">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -428,6 +428,9 @@
       </rPr>
       <t xml:space="preserve"> Martes y Jueves en ausencia de Juan Jose</t>
     </r>
+  </si>
+  <si>
+    <t>Seguimiento Juego Comando - Proveedor Andes Gaming - Cada hora</t>
   </si>
 </sst>
 </file>
@@ -762,45 +765,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="104">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="102">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3009,130 +2992,130 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="103" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="102" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="101" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="100" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B31">
-    <cfRule type="duplicateValues" dxfId="99" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="98" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B34 B9">
-    <cfRule type="duplicateValues" dxfId="97" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B29 B11">
-    <cfRule type="duplicateValues" dxfId="96" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="95" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="94" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="93" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="92" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="91" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="90" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="89" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="88" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="duplicateValues" dxfId="87" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="86" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="85" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="84" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="83" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="82" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="duplicateValues" dxfId="81" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H26">
-    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="duplicateValues" dxfId="79" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="duplicateValues" dxfId="78" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="77" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="76" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="75" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="74" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="73" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="72" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="71" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="70" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="69" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="duplicateValues" dxfId="68" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="duplicateValues" dxfId="67" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="duplicateValues" dxfId="66" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="23"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4159,91 +4142,91 @@
     <mergeCell ref="K18:L18"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="65" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="64" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="63" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12 B15">
-    <cfRule type="duplicateValues" dxfId="62" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B31">
-    <cfRule type="duplicateValues" dxfId="61" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="60" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="59" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34 B29 B11">
-    <cfRule type="duplicateValues" dxfId="58" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="57" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="56" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="55" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="54" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="53" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="52" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="51" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="50" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23">
-    <cfRule type="duplicateValues" dxfId="49" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="47" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="46" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="45" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="44" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="43" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="42" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24">
-    <cfRule type="duplicateValues" dxfId="41" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K26">
-    <cfRule type="duplicateValues" dxfId="40" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="duplicateValues" dxfId="38" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="duplicateValues" dxfId="37" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4284,25 +4267,25 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="23"/>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="39"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="38" t="s">
+      <c r="E2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="39"/>
+      <c r="F2" s="43"/>
       <c r="G2" s="23"/>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="39"/>
+      <c r="I2" s="43"/>
       <c r="J2" s="23"/>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="39"/>
+      <c r="L2" s="43"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="23"/>
@@ -4714,16 +4697,16 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="23"/>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="39"/>
+      <c r="C17" s="43"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="40"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="39"/>
       <c r="H17" s="37"/>
       <c r="I17" s="23"/>
       <c r="J17" s="37"/>
@@ -4746,15 +4729,15 @@
         <v>5</v>
       </c>
       <c r="G18" s="23"/>
-      <c r="H18" s="38" t="s">
+      <c r="H18" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="39"/>
+      <c r="I18" s="43"/>
       <c r="J18" s="23"/>
-      <c r="K18" s="38" t="s">
+      <c r="K18" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="39"/>
+      <c r="L18" s="43"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="23"/>
@@ -4884,7 +4867,7 @@
       <c r="C23" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="40"/>
+      <c r="D23" s="39"/>
       <c r="E23" s="37"/>
       <c r="F23" s="24"/>
       <c r="G23" s="23"/>
@@ -4910,7 +4893,7 @@
       <c r="C24" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="40"/>
+      <c r="D24" s="39"/>
       <c r="E24" s="37"/>
       <c r="F24" s="24"/>
       <c r="G24" s="23"/>
@@ -4936,7 +4919,7 @@
       <c r="C25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="40"/>
+      <c r="D25" s="39"/>
       <c r="E25" s="37"/>
       <c r="F25" s="24"/>
       <c r="G25" s="23"/>
@@ -4978,11 +4961,11 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="23"/>
-      <c r="B27" s="38" t="s">
+      <c r="B27" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="40"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="39"/>
       <c r="E27" s="37"/>
       <c r="F27" s="24"/>
       <c r="G27" s="23"/>
@@ -5008,7 +4991,7 @@
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="40"/>
+      <c r="D28" s="39"/>
       <c r="E28" s="37"/>
       <c r="F28" s="24"/>
       <c r="G28" s="23"/>
@@ -5034,7 +5017,7 @@
       <c r="C29" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="40"/>
+      <c r="D29" s="39"/>
       <c r="E29" s="37"/>
       <c r="F29" s="24"/>
       <c r="G29" s="23"/>
@@ -5060,7 +5043,7 @@
       <c r="C30" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="40"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="37"/>
       <c r="F30" s="24"/>
       <c r="G30" s="23"/>
@@ -5086,7 +5069,7 @@
       <c r="C31" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="40"/>
+      <c r="D31" s="39"/>
       <c r="E31" s="37"/>
       <c r="F31" s="24"/>
       <c r="G31" s="37"/>
@@ -5104,19 +5087,19 @@
       <c r="C32" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="42"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="38"/>
       <c r="F32" s="24"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="38" t="s">
+      <c r="H32" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="43"/>
+      <c r="I32" s="42"/>
       <c r="J32" s="23"/>
-      <c r="K32" s="38" t="s">
+      <c r="K32" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="39"/>
+      <c r="L32" s="43"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="23"/>
@@ -5126,8 +5109,8 @@
       <c r="C33" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="42"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="38"/>
       <c r="F33" s="24"/>
       <c r="G33" s="23"/>
       <c r="H33" s="3" t="s">
@@ -5152,8 +5135,8 @@
       <c r="C34" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="41"/>
-      <c r="E34" s="42"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="38"/>
       <c r="F34" s="24"/>
       <c r="G34" s="23"/>
       <c r="H34" s="9" t="s">
@@ -5178,8 +5161,8 @@
       <c r="C35" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="41"/>
-      <c r="E35" s="42"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="38"/>
       <c r="F35" s="24"/>
       <c r="G35" s="23"/>
       <c r="H35" s="9" t="s">
@@ -5204,8 +5187,8 @@
       <c r="C36" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="38"/>
       <c r="F36" s="24"/>
       <c r="G36" s="23"/>
       <c r="H36" s="9" t="s">
@@ -5230,8 +5213,8 @@
       <c r="C37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="41"/>
-      <c r="E37" s="42"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="38"/>
       <c r="F37" s="24"/>
       <c r="G37" s="23"/>
       <c r="H37" s="9" t="s">
@@ -5252,8 +5235,8 @@
       <c r="A38" s="37"/>
       <c r="B38" s="37"/>
       <c r="C38" s="24"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
       <c r="F38" s="24"/>
       <c r="G38" s="23"/>
       <c r="H38" s="9" t="s">
@@ -5274,8 +5257,8 @@
       <c r="A39" s="37"/>
       <c r="B39" s="37"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
       <c r="F39" s="24"/>
       <c r="G39" s="37"/>
       <c r="H39" s="37"/>
@@ -5288,8 +5271,8 @@
       <c r="A40" s="37"/>
       <c r="B40" s="37"/>
       <c r="C40" s="24"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
       <c r="F40" s="24"/>
       <c r="G40" s="37"/>
       <c r="H40" s="37"/>
@@ -5302,8 +5285,8 @@
       <c r="A41" s="37"/>
       <c r="B41" s="37"/>
       <c r="C41" s="24"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
       <c r="F41" s="24"/>
       <c r="G41" s="37"/>
       <c r="H41" s="37"/>
@@ -5314,6 +5297,46 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="G41:H41"/>
@@ -5326,72 +5349,32 @@
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="J40:K40"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42A8CB2C-D9C5-4429-9B06-5F24BAC192A6}">
-  <dimension ref="B2:L39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA7AB0E-EBB4-4E28-B41F-E76E04CDE1BD}">
+  <dimension ref="B2:L40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="3.3984375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="93.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="93.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.3984375" style="2" customWidth="1"/>
     <col min="5" max="5" width="52.3984375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.59765625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="52.59765625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.796875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="61.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.69921875" style="2" customWidth="1"/>
     <col min="10" max="10" width="5.59765625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="55" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="61.8984375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="11.59765625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12">
+    <row r="2" spans="2:12" s="2" customFormat="1">
       <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
@@ -5410,7 +5393,7 @@
       </c>
       <c r="L2" s="34"/>
     </row>
-    <row r="3" spans="2:12" ht="14.4">
+    <row r="3" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B3" s="31" t="s">
         <v>4</v>
       </c>
@@ -5437,7 +5420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="14.4">
+    <row r="4" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -5463,7 +5446,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="14.4">
+    <row r="5" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -5489,7 +5472,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="14.4">
+    <row r="6" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -5515,7 +5498,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="14.4">
+    <row r="7" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -5541,7 +5524,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="14.4">
+    <row r="8" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -5567,7 +5550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="14.4">
+    <row r="9" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -5593,7 +5576,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="14.4">
+    <row r="10" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -5619,7 +5602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="14.4">
+    <row r="11" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B11" s="8" t="s">
         <v>30</v>
       </c>
@@ -5645,7 +5628,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="14.4">
+    <row r="12" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B12" s="6" t="s">
         <v>36</v>
       </c>
@@ -5671,7 +5654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="14.4">
+    <row r="13" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B13" s="8" t="s">
         <v>103</v>
       </c>
@@ -5698,7 +5681,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="14.4">
+    <row r="14" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B14" s="8" t="s">
         <v>104</v>
       </c>
@@ -5725,7 +5708,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="14.4">
+    <row r="15" spans="2:12" s="2" customFormat="1" ht="14.4">
+      <c r="C15" s="1"/>
       <c r="E15" s="6" t="s">
         <v>36</v>
       </c>
@@ -5745,7 +5729,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="14.4">
+    <row r="16" spans="2:12" s="2" customFormat="1" ht="14.4">
+      <c r="C16" s="1"/>
       <c r="E16" s="6" t="s">
         <v>44</v>
       </c>
@@ -5753,44 +5738,36 @@
         <v>45</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16" s="8" t="s">
-        <v>79</v>
+      <c r="H16" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="I16" s="32" t="s">
         <v>45</v>
       </c>
       <c r="J16" s="1"/>
-      <c r="K16" s="8" t="s">
-        <v>79</v>
+      <c r="K16" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:12">
+    <row r="17" spans="2:12" s="2" customFormat="1">
       <c r="B17" s="34" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="34"/>
-    </row>
-    <row r="18" spans="2:12" ht="14.4">
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B18" s="31" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="H18" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="34"/>
-      <c r="K18" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="L18" s="34"/>
-    </row>
-    <row r="19" spans="2:12" ht="14.4">
+    </row>
+    <row r="19" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B19" s="6" t="s">
         <v>12</v>
       </c>
@@ -5801,20 +5778,16 @@
         <v>95</v>
       </c>
       <c r="F19" s="34"/>
-      <c r="H19" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="I19" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="K19" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="L19" s="33" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" ht="14.4">
+      <c r="H19" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="34"/>
+      <c r="K19" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="L19" s="34"/>
+    </row>
+    <row r="20" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B20" s="6" t="s">
         <v>16</v>
       </c>
@@ -5827,20 +5800,20 @@
       <c r="F20" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="14.4">
+      <c r="H20" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B21" s="6" t="s">
         <v>23</v>
       </c>
@@ -5854,19 +5827,19 @@
         <v>40</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="I21" s="32" t="s">
         <v>13</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="14.4">
+    <row r="22" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B22" s="6" t="s">
         <v>26</v>
       </c>
@@ -5880,19 +5853,19 @@
         <v>40</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="I22" s="32" t="s">
         <v>13</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>97</v>
+        <v>16</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="2:12" ht="14.4">
+    <row r="23" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B23" s="8" t="s">
         <v>18</v>
       </c>
@@ -5906,19 +5879,19 @@
         <v>40</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="I23" s="32" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="27.6">
+    <row r="24" spans="2:12" s="2" customFormat="1" ht="27.6">
       <c r="B24" s="8" t="s">
         <v>31</v>
       </c>
@@ -5932,140 +5905,160 @@
         <v>40</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I24" s="32" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="14.4">
+    <row r="25" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B25" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C25" s="32" t="s">
         <v>33</v>
       </c>
+      <c r="F25" s="1"/>
       <c r="H25" s="12" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="I25" s="32" t="s">
         <v>13</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="14.4">
+    <row r="26" spans="2:12" s="2" customFormat="1" ht="14.4">
+      <c r="C26" s="1"/>
+      <c r="F26" s="1"/>
       <c r="H26" s="12" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="I26" s="32" t="s">
         <v>13</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:12" ht="14.4">
+    <row r="27" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B27" s="34" t="s">
         <v>38</v>
       </c>
       <c r="C27" s="34"/>
+      <c r="F27" s="1"/>
       <c r="H27" s="12" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I27" s="32" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="2:12" ht="14.4">
+    <row r="28" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B28" s="31" t="s">
         <v>4</v>
       </c>
       <c r="C28" s="31" t="s">
         <v>5</v>
       </c>
+      <c r="F28" s="1"/>
       <c r="H28" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I28" s="32" t="s">
         <v>13</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="2:12" ht="14.4">
+    <row r="29" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B29" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="F29" s="1"/>
       <c r="H29" s="12" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="I29" s="32" t="s">
         <v>13</v>
       </c>
       <c r="K29" s="12" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="14.4">
+    <row r="30" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B30" s="17" t="s">
         <v>35</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H30" s="8" t="s">
-        <v>79</v>
+      <c r="F30" s="1"/>
+      <c r="H30" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="I30" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="J30" s="1"/>
-      <c r="K30" s="8" t="s">
-        <v>79</v>
+      <c r="K30" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="2:12">
+    <row r="31" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B31" s="8" t="s">
         <v>79</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" spans="2:12">
+      <c r="F31" s="1"/>
+      <c r="H31" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I31" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B32" s="6" t="s">
         <v>22</v>
       </c>
@@ -6073,16 +6066,22 @@
         <v>14</v>
       </c>
       <c r="D32"/>
-      <c r="H32" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="I32" s="36"/>
-      <c r="K32" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="L32" s="34"/>
-    </row>
-    <row r="33" spans="2:12" ht="14.4">
+      <c r="F32" s="1"/>
+      <c r="H32" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="I32" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" s="2" customFormat="1">
       <c r="B33" s="6" t="s">
         <v>42</v>
       </c>
@@ -6090,20 +6089,9 @@
         <v>14</v>
       </c>
       <c r="D33"/>
-      <c r="H33" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="I33" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="L33" s="31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12">
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="2:12" s="2" customFormat="1">
       <c r="B34" s="6" t="s">
         <v>42</v>
       </c>
@@ -6111,20 +6099,17 @@
         <v>8</v>
       </c>
       <c r="D34"/>
-      <c r="H34" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12">
+      <c r="F34" s="1"/>
+      <c r="H34" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="I34" s="36"/>
+      <c r="K34" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="L34" s="34"/>
+    </row>
+    <row r="35" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B35" s="8" t="s">
         <v>41</v>
       </c>
@@ -6132,20 +6117,21 @@
         <v>8</v>
       </c>
       <c r="D35"/>
-      <c r="H35" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12">
+      <c r="F35" s="1"/>
+      <c r="H35" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="L35" s="31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" s="2" customFormat="1">
       <c r="B36" s="13" t="s">
         <v>80</v>
       </c>
@@ -6153,177 +6139,210 @@
         <v>8</v>
       </c>
       <c r="D36"/>
+      <c r="F36" s="1"/>
       <c r="H36" s="6" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="2:12">
+    <row r="37" spans="2:12" s="2" customFormat="1">
+      <c r="B37" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D37"/>
+      <c r="F37" s="1"/>
       <c r="H37" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="2:12">
+    <row r="38" spans="2:12" s="2" customFormat="1">
+      <c r="C38" s="1"/>
       <c r="D38"/>
+      <c r="F38" s="1"/>
       <c r="H38" s="6" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>40</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="2:12">
+    <row r="39" spans="2:12" s="2" customFormat="1">
+      <c r="C39" s="1"/>
       <c r="D39"/>
+      <c r="F39" s="1"/>
+      <c r="H39" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" s="2" customFormat="1">
+      <c r="C40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="H40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="d7vKTB1NsKMzTP3OJzvu/ePVtZYm0laOc19cvVp4GYSG6Ps8to4DQt2UeZgMqFeJ7HXLpxvodTZ7LAlW0JWT+Q==" saltValue="KW8KYlaKpYzqhnMAW6lRXg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="K34:L34"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="B27:C27"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="H19:I19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="36" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="35" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="34" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9 B33:B34">
-    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12 B15">
-    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B31">
-    <cfRule type="duplicateValues" dxfId="31" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B29 B11">
-    <cfRule type="duplicateValues" dxfId="29" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="28" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="25" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="23" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15 E17">
-    <cfRule type="duplicateValues" dxfId="21" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24">
-    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="19" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H25:H26">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H30">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H37">
-    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="10" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H25">
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H26:H27">
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H39">
+    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H40">
+    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="7" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="6" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K24">
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K25:K26">
-    <cfRule type="duplicateValues" dxfId="3" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K30">
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K37">
-    <cfRule type="duplicateValues" dxfId="1" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K38">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K25">
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K26:K27">
+    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K31">
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K39">
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K40">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6545,12 +6564,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6755,15 +6771,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6788,10 +6808,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://virtualsoftserv-my.sharepoint.com/personal/luis_fuentes_virtualsoft_tech/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{94C845A1-4725-47C1-B6E7-67D7B6C838DB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{B4F5BB62-2075-44F6-80BA-4B8BF413BC82}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A99AA2-E29B-4877-9DD5-7F92E48F9B28}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
     <sheet name="Semana 2 - 7 Sep al 13 Sep" sheetId="9" r:id="rId2"/>
     <sheet name="Semana 3 - 14 al 20 Sep" sheetId="15" r:id="rId3"/>
-    <sheet name="Semana 4 - 21 Sep al 04 Oct" sheetId="17" r:id="rId4"/>
+    <sheet name="Semana 4 - 21 al 27 Sep" sheetId="19" r:id="rId4"/>
     <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="107">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -432,12 +432,15 @@
   <si>
     <t>Seguimiento Juego Comando - Proveedor Andes Gaming - Cada hora</t>
   </si>
+  <si>
+    <t>Revisión RiskLive (Usuarios que cruzaron en Pragmatic)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -508,17 +511,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -658,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -744,15 +736,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -765,18 +748,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2153,23 +2142,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" s="2" customFormat="1">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="34"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="34"/>
-      <c r="H2" s="34" t="s">
+      <c r="F2" s="31"/>
+      <c r="H2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="34"/>
-      <c r="K2" s="34" t="s">
+      <c r="I2" s="31"/>
+      <c r="K2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="34"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B3" s="3" t="s">
@@ -2524,14 +2513,14 @@
       </c>
     </row>
     <row r="17" spans="2:12" s="2" customFormat="1">
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="E17" s="34" t="s">
+      <c r="C17" s="31"/>
+      <c r="E17" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="34"/>
+      <c r="F17" s="31"/>
     </row>
     <row r="18" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B18" s="3" t="s">
@@ -2546,14 +2535,14 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="34" t="s">
+      <c r="H18" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="34"/>
-      <c r="K18" s="34" t="s">
+      <c r="I18" s="31"/>
+      <c r="K18" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="34"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" spans="2:12" s="2" customFormat="1" ht="28.95" customHeight="1">
       <c r="B19" s="6" t="s">
@@ -2839,14 +2828,14 @@
       </c>
       <c r="D32"/>
       <c r="F32" s="1"/>
-      <c r="H32" s="35" t="s">
+      <c r="H32" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="36"/>
-      <c r="K32" s="34" t="s">
+      <c r="I32" s="33"/>
+      <c r="K32" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="31"/>
     </row>
     <row r="33" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B33" s="6" t="s">
@@ -2992,16 +2981,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="101" priority="35"/>
@@ -3153,25 +3142,25 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2"/>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="34"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="34"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="34"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="34"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="2"/>
@@ -3587,10 +3576,10 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2"/>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="34"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="G17" s="2"/>
@@ -3609,20 +3598,20 @@
         <v>5</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="34"/>
+      <c r="F18" s="31"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="34" t="s">
+      <c r="H18" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="34"/>
+      <c r="I18" s="31"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="34" t="s">
+      <c r="K18" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="34"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="2"/>
@@ -3850,10 +3839,10 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2"/>
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="34"/>
+      <c r="C27" s="31"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="1"/>
@@ -3979,15 +3968,15 @@
       <c r="E32" s="2"/>
       <c r="F32" s="1"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="35" t="s">
+      <c r="H32" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="36"/>
+      <c r="I32" s="33"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="34" t="s">
+      <c r="K32" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="31"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="2"/>
@@ -4252,40 +4241,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
+      <c r="A1" s="34"/>
+      <c r="B1" s="34"/>
       <c r="C1" s="24"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
       <c r="I1" s="23"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
       <c r="L1" s="23"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="23"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="43"/>
+      <c r="C2" s="36"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="43"/>
+      <c r="F2" s="36"/>
       <c r="G2" s="23"/>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="43"/>
+      <c r="I2" s="36"/>
       <c r="J2" s="23"/>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="43"/>
+      <c r="L2" s="36"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="23"/>
@@ -4648,8 +4637,8 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="14.4">
-      <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="34"/>
       <c r="C15" s="24"/>
       <c r="D15" s="23"/>
       <c r="E15" s="9" t="s">
@@ -4674,11 +4663,11 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="14.4">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="19" t="s">
@@ -4697,20 +4686,20 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="23"/>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="43"/>
+      <c r="C17" s="36"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="37"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="34"/>
       <c r="I17" s="23"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
       <c r="L17" s="23"/>
     </row>
     <row r="18" spans="1:12" ht="14.4">
@@ -4729,15 +4718,15 @@
         <v>5</v>
       </c>
       <c r="G18" s="23"/>
-      <c r="H18" s="41" t="s">
+      <c r="H18" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="43"/>
+      <c r="I18" s="36"/>
       <c r="J18" s="23"/>
-      <c r="K18" s="41" t="s">
+      <c r="K18" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="43"/>
+      <c r="L18" s="36"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="23"/>
@@ -4867,8 +4856,8 @@
       <c r="C23" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="39"/>
-      <c r="E23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="34"/>
       <c r="F23" s="24"/>
       <c r="G23" s="23"/>
       <c r="H23" s="10" t="s">
@@ -4893,8 +4882,8 @@
       <c r="C24" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="39"/>
-      <c r="E24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="34"/>
       <c r="F24" s="24"/>
       <c r="G24" s="23"/>
       <c r="H24" s="10" t="s">
@@ -4919,8 +4908,8 @@
       <c r="C25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="39"/>
-      <c r="E25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="34"/>
       <c r="F25" s="24"/>
       <c r="G25" s="23"/>
       <c r="H25" s="10" t="s">
@@ -4938,11 +4927,11 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="14.4">
-      <c r="A26" s="37"/>
-      <c r="B26" s="37"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="24"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="24"/>
       <c r="G26" s="23"/>
       <c r="H26" s="10" t="s">
@@ -4961,12 +4950,12 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="23"/>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="37"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="34"/>
       <c r="F27" s="24"/>
       <c r="G27" s="23"/>
       <c r="H27" s="10" t="s">
@@ -4991,8 +4980,8 @@
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="39"/>
-      <c r="E28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="34"/>
       <c r="F28" s="24"/>
       <c r="G28" s="23"/>
       <c r="H28" s="10" t="s">
@@ -5017,8 +5006,8 @@
       <c r="C29" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="39"/>
-      <c r="E29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="34"/>
       <c r="F29" s="24"/>
       <c r="G29" s="23"/>
       <c r="H29" s="10" t="s">
@@ -5043,8 +5032,8 @@
       <c r="C30" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="34"/>
       <c r="F30" s="24"/>
       <c r="G30" s="23"/>
       <c r="H30" s="22" t="s">
@@ -5069,14 +5058,14 @@
       <c r="C31" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="39"/>
-      <c r="E31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="34"/>
       <c r="F31" s="24"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
       <c r="I31" s="23"/>
-      <c r="J31" s="37"/>
-      <c r="K31" s="37"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="34"/>
       <c r="L31" s="23"/>
     </row>
     <row r="32" spans="1:12">
@@ -5087,19 +5076,19 @@
       <c r="C32" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="40"/>
-      <c r="E32" s="38"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="39"/>
       <c r="F32" s="24"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="41" t="s">
+      <c r="H32" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="42"/>
+      <c r="I32" s="40"/>
       <c r="J32" s="23"/>
-      <c r="K32" s="41" t="s">
+      <c r="K32" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="43"/>
+      <c r="L32" s="36"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="23"/>
@@ -5109,8 +5098,8 @@
       <c r="C33" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="40"/>
-      <c r="E33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="39"/>
       <c r="F33" s="24"/>
       <c r="G33" s="23"/>
       <c r="H33" s="3" t="s">
@@ -5135,8 +5124,8 @@
       <c r="C34" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="40"/>
-      <c r="E34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="39"/>
       <c r="F34" s="24"/>
       <c r="G34" s="23"/>
       <c r="H34" s="9" t="s">
@@ -5161,8 +5150,8 @@
       <c r="C35" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="40"/>
-      <c r="E35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="39"/>
       <c r="F35" s="24"/>
       <c r="G35" s="23"/>
       <c r="H35" s="9" t="s">
@@ -5187,8 +5176,8 @@
       <c r="C36" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="40"/>
-      <c r="E36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="39"/>
       <c r="F36" s="24"/>
       <c r="G36" s="23"/>
       <c r="H36" s="9" t="s">
@@ -5213,8 +5202,8 @@
       <c r="C37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="40"/>
-      <c r="E37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="39"/>
       <c r="F37" s="24"/>
       <c r="G37" s="23"/>
       <c r="H37" s="9" t="s">
@@ -5232,11 +5221,11 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="37"/>
-      <c r="B38" s="37"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="34"/>
       <c r="C38" s="24"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
       <c r="F38" s="24"/>
       <c r="G38" s="23"/>
       <c r="H38" s="9" t="s">
@@ -5254,89 +5243,49 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="37"/>
-      <c r="B39" s="37"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="34"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="39"/>
       <c r="F39" s="24"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
       <c r="I39" s="23"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="37"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
       <c r="L39" s="23"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="37"/>
-      <c r="B40" s="37"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="34"/>
       <c r="C40" s="24"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
       <c r="F40" s="24"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="34"/>
       <c r="I40" s="23"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="37"/>
+      <c r="J40" s="34"/>
+      <c r="K40" s="34"/>
       <c r="L40" s="23"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="37"/>
-      <c r="B41" s="37"/>
+      <c r="A41" s="34"/>
+      <c r="B41" s="34"/>
       <c r="C41" s="24"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
       <c r="F41" s="24"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
       <c r="I41" s="23"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="37"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
       <c r="L41" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="G41:H41"/>
@@ -5349,13 +5298,53 @@
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="J40:K40"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA7AB0E-EBB4-4E28-B41F-E76E04CDE1BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0797C7-DA66-4603-8F20-80D6408B720F}">
   <dimension ref="B2:L40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
   <cols>
@@ -5374,53 +5363,53 @@
     <col min="13" max="16384" width="11.59765625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" s="2" customFormat="1">
-      <c r="B2" s="34" t="s">
+    <row r="2" spans="2:12">
+      <c r="B2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="34"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="34"/>
-      <c r="H2" s="34" t="s">
+      <c r="F2" s="31"/>
+      <c r="H2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="34"/>
-      <c r="K2" s="34" t="s">
+      <c r="I2" s="31"/>
+      <c r="K2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="34"/>
-    </row>
-    <row r="3" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="B3" s="31" t="s">
+      <c r="L2" s="31"/>
+    </row>
+    <row r="3" spans="2:12" ht="14.4">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="31" t="s">
+      <c r="I3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="31" t="s">
+      <c r="K3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="4" spans="2:12" ht="14.4">
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
@@ -5436,7 +5425,7 @@
       <c r="H4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="I4" s="7" t="s">
         <v>45</v>
       </c>
       <c r="K4" s="6" t="s">
@@ -5446,7 +5435,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="5" spans="2:12" ht="14.4">
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
@@ -5472,7 +5461,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="6" spans="2:12" ht="14.4">
       <c r="B6" s="6" t="s">
         <v>9</v>
       </c>
@@ -5488,7 +5477,7 @@
       <c r="H6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="I6" s="7" t="s">
         <v>45</v>
       </c>
       <c r="K6" s="6" t="s">
@@ -5498,7 +5487,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="7" spans="2:12" ht="14.4">
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
@@ -5524,7 +5513,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="8" spans="2:12" ht="14.4">
       <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
@@ -5540,7 +5529,7 @@
       <c r="H8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I8" s="7" t="s">
         <v>45</v>
       </c>
       <c r="K8" s="4" t="s">
@@ -5550,7 +5539,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="9" spans="2:12" ht="14.4">
       <c r="B9" s="6" t="s">
         <v>20</v>
       </c>
@@ -5576,7 +5565,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="10" spans="2:12" ht="14.4">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -5592,7 +5581,7 @@
       <c r="H10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" s="7" t="s">
         <v>45</v>
       </c>
       <c r="K10" s="6" t="s">
@@ -5602,7 +5591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="11" spans="2:12" ht="14.4">
       <c r="B11" s="8" t="s">
         <v>30</v>
       </c>
@@ -5628,7 +5617,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="12" spans="2:12" ht="14.4">
       <c r="B12" s="6" t="s">
         <v>36</v>
       </c>
@@ -5644,7 +5633,7 @@
       <c r="H12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="7" t="s">
         <v>45</v>
       </c>
       <c r="K12" s="6" t="s">
@@ -5654,7 +5643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="13" spans="2:12" ht="14.4">
       <c r="B13" s="8" t="s">
         <v>103</v>
       </c>
@@ -5681,7 +5670,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="14" spans="2:12" ht="14.4">
       <c r="B14" s="8" t="s">
         <v>104</v>
       </c>
@@ -5698,7 +5687,7 @@
       <c r="H14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="32" t="s">
+      <c r="I14" s="7" t="s">
         <v>45</v>
       </c>
       <c r="K14" s="9" t="s">
@@ -5708,8 +5697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="C15" s="1"/>
+    <row r="15" spans="2:12" ht="14.4">
       <c r="E15" s="6" t="s">
         <v>36</v>
       </c>
@@ -5729,8 +5717,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="C16" s="1"/>
+    <row r="16" spans="2:12" ht="14.4">
       <c r="E16" s="6" t="s">
         <v>44</v>
       </c>
@@ -5741,7 +5728,7 @@
       <c r="H16" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="I16" s="7" t="s">
         <v>45</v>
       </c>
       <c r="J16" s="1"/>
@@ -5752,72 +5739,72 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:12" s="2" customFormat="1">
-      <c r="B17" s="34" t="s">
+    <row r="17" spans="2:12">
+      <c r="B17" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="B18" s="31" t="s">
+      <c r="C17" s="31"/>
+    </row>
+    <row r="18" spans="2:12" ht="14.4">
+      <c r="B18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="2:12" s="2" customFormat="1" ht="14.4">
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="2:12" ht="14.4">
       <c r="B19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="32" t="s">
+      <c r="C19" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="F19" s="34"/>
-      <c r="H19" s="34" t="s">
+      <c r="F19" s="31"/>
+      <c r="H19" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="34"/>
-      <c r="K19" s="34" t="s">
+      <c r="I19" s="31"/>
+      <c r="K19" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="L19" s="34"/>
-    </row>
-    <row r="20" spans="2:12" s="2" customFormat="1" ht="14.4">
+      <c r="L19" s="31"/>
+    </row>
+    <row r="20" spans="2:12" ht="14.4">
       <c r="B20" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="31" t="s">
+      <c r="H20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I20" s="31" t="s">
+      <c r="I20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="31" t="s">
+      <c r="K20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L20" s="33" t="s">
+      <c r="L20" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="21" spans="2:12" ht="14.4">
       <c r="B21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E21" s="6" t="s">
@@ -5829,7 +5816,7 @@
       <c r="H21" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="I21" s="32" t="s">
+      <c r="I21" s="7" t="s">
         <v>13</v>
       </c>
       <c r="K21" s="12" t="s">
@@ -5839,11 +5826,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="22" spans="2:12" ht="14.4">
       <c r="B22" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E22" s="6" t="s">
@@ -5855,7 +5842,7 @@
       <c r="H22" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="32" t="s">
+      <c r="I22" s="7" t="s">
         <v>13</v>
       </c>
       <c r="K22" s="12" t="s">
@@ -5865,11 +5852,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="23" spans="2:12" ht="14.4">
       <c r="B23" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="6" t="s">
@@ -5881,7 +5868,7 @@
       <c r="H23" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="I23" s="32" t="s">
+      <c r="I23" s="7" t="s">
         <v>13</v>
       </c>
       <c r="K23" s="12" t="s">
@@ -5891,11 +5878,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="2:12" s="2" customFormat="1" ht="27.6">
+    <row r="24" spans="2:12" ht="27.6">
       <c r="B24" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E24" s="6" t="s">
@@ -5907,7 +5894,7 @@
       <c r="H24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I24" s="32" t="s">
+      <c r="I24" s="7" t="s">
         <v>13</v>
       </c>
       <c r="K24" s="12" t="s">
@@ -5917,18 +5904,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="25" spans="2:12" ht="14.4">
       <c r="B25" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="1"/>
       <c r="H25" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I25" s="32" t="s">
+      <c r="I25" s="7" t="s">
         <v>13</v>
       </c>
       <c r="K25" s="12" t="s">
@@ -5938,13 +5924,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="C26" s="1"/>
-      <c r="F26" s="1"/>
+    <row r="26" spans="2:12" ht="14.4">
+      <c r="B26" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="H26" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="I26" s="32" t="s">
+      <c r="I26" s="7" t="s">
         <v>13</v>
       </c>
       <c r="K26" s="12" t="s">
@@ -5954,16 +5944,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="B27" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="34"/>
-      <c r="F27" s="1"/>
+    <row r="27" spans="2:12" ht="14.4">
+      <c r="B27" s="41"/>
+      <c r="C27" s="42"/>
       <c r="H27" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="32" t="s">
+      <c r="I27" s="7" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="12" t="s">
@@ -5973,18 +5960,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="B28" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" s="1"/>
+    <row r="28" spans="2:12" ht="14.4">
       <c r="H28" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="32" t="s">
+      <c r="I28" s="7" t="s">
         <v>13</v>
       </c>
       <c r="K28" s="12" t="s">
@@ -5994,18 +5974,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="B29" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="1"/>
+    <row r="29" spans="2:12" ht="14.4">
+      <c r="B29" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="31"/>
       <c r="H29" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I29" s="32" t="s">
+      <c r="I29" s="7" t="s">
         <v>13</v>
       </c>
       <c r="K29" s="12" t="s">
@@ -6015,18 +5992,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="B30" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" s="1"/>
+    <row r="30" spans="2:12" ht="14.4">
+      <c r="B30" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="H30" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="I30" s="32" t="s">
+      <c r="I30" s="7" t="s">
         <v>13</v>
       </c>
       <c r="K30" s="12" t="s">
@@ -6036,18 +6012,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="2:12" s="2" customFormat="1" ht="14.4">
+    <row r="31" spans="2:12" ht="14.4">
       <c r="B31" s="8" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="1"/>
       <c r="H31" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="I31" s="32" t="s">
+      <c r="I31" s="7" t="s">
         <v>13</v>
       </c>
       <c r="J31" s="1"/>
@@ -6058,19 +6033,18 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="B32" s="6" t="s">
-        <v>22</v>
+    <row r="32" spans="2:12" ht="14.4">
+      <c r="B32" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D32"/>
-      <c r="F32" s="1"/>
       <c r="H32" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="I32" s="32" t="s">
+      <c r="I32" s="7" t="s">
         <v>13</v>
       </c>
       <c r="J32" s="1"/>
@@ -6081,65 +6055,61 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="2:12" s="2" customFormat="1">
-      <c r="B33" s="6" t="s">
-        <v>42</v>
+    <row r="33" spans="2:12">
+      <c r="B33" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D33"/>
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="2:12" s="2" customFormat="1">
+    </row>
+    <row r="34" spans="2:12">
       <c r="B34" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D34"/>
+      <c r="H34" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="I34" s="33"/>
+      <c r="K34" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="L34" s="31"/>
+    </row>
+    <row r="35" spans="2:12" ht="14.4">
+      <c r="B35" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34"/>
-      <c r="F34" s="1"/>
-      <c r="H34" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="I34" s="36"/>
-      <c r="K34" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="L34" s="34"/>
-    </row>
-    <row r="35" spans="2:12" s="2" customFormat="1" ht="14.4">
-      <c r="B35" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="C35" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D35"/>
-      <c r="F35" s="1"/>
-      <c r="H35" s="31" t="s">
+      <c r="H35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I35" s="31" t="s">
+      <c r="I35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K35" s="31" t="s">
+      <c r="K35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L35" s="31" t="s">
+      <c r="L35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="2:12" s="2" customFormat="1">
-      <c r="B36" s="13" t="s">
-        <v>80</v>
+    <row r="36" spans="2:12">
+      <c r="B36" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D36"/>
-      <c r="F36" s="1"/>
       <c r="H36" s="6" t="s">
         <v>12</v>
       </c>
@@ -6153,15 +6123,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="2:12" s="2" customFormat="1">
-      <c r="B37" s="19" t="s">
-        <v>105</v>
+    <row r="37" spans="2:12">
+      <c r="B37" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D37"/>
-      <c r="F37" s="1"/>
       <c r="H37" s="6" t="s">
         <v>16</v>
       </c>
@@ -6175,10 +6144,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="2:12" s="2" customFormat="1">
-      <c r="C38" s="1"/>
+    <row r="38" spans="2:12">
+      <c r="B38" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D38"/>
-      <c r="F38" s="1"/>
       <c r="H38" s="6" t="s">
         <v>43</v>
       </c>
@@ -6192,10 +6165,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="2:12" s="2" customFormat="1">
-      <c r="C39" s="1"/>
+    <row r="39" spans="2:12">
+      <c r="B39" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D39"/>
-      <c r="F39" s="1"/>
       <c r="H39" s="6" t="s">
         <v>22</v>
       </c>
@@ -6209,9 +6186,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="2:12" s="2" customFormat="1">
-      <c r="C40" s="1"/>
-      <c r="F40" s="1"/>
+    <row r="40" spans="2:12">
       <c r="H40" s="6" t="s">
         <v>21</v>
       </c>
@@ -6226,18 +6201,19 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="EuO9at0TXMwgajATRRwMQok4w72EQ4ahdYJ+6J3w7mQdEsRr6kNEB9B6jgIce5y+0FTqsYhoMaaQ6QUsEJuxHA==" saltValue="TM0jAjYbq8HFQYXEp7A2hQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
-    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="K34:L34"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E19:F19"/>
     <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="34" priority="30"/>
@@ -6248,19 +6224,19 @@
   <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="32" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9 B33:B34">
+  <conditionalFormatting sqref="B35:B36 B9">
     <cfRule type="duplicateValues" dxfId="31" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12 B15">
     <cfRule type="duplicateValues" dxfId="30" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B25 B31">
+  <conditionalFormatting sqref="B33 B25:B27">
     <cfRule type="duplicateValues" dxfId="29" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32 B10">
+  <conditionalFormatting sqref="B34 B10">
     <cfRule type="duplicateValues" dxfId="28" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35 B29 B11">
+  <conditionalFormatting sqref="B37 B31 B11">
     <cfRule type="duplicateValues" dxfId="27" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
@@ -6564,9 +6540,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6771,19 +6750,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6808,9 +6783,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A99AA2-E29B-4877-9DD5-7F92E48F9B28}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD4589F-0177-494E-BD95-9C38BE377AF0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
     <sheet name="Semana 2 - 7 Sep al 13 Sep" sheetId="9" r:id="rId2"/>
     <sheet name="Semana 3 - 14 al 20 Sep" sheetId="15" r:id="rId3"/>
-    <sheet name="Semana 4 - 21 al 27 Sep" sheetId="19" r:id="rId4"/>
+    <sheet name="Semana 4 - 21 al 27 Sep" sheetId="20" r:id="rId4"/>
     <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="105">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -397,36 +397,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>lunes y Martes hasta 1:00pm y Miercoles y Jueves hasta las 11:00am, en ausencia de Josue</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Apoyo Revisión GGR negativo casino / deportivo//</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Martes y Jueves en ausencia de Juan Jose</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Apoyo Deltas (Registros, Bonos, Premios Bonos y Bonos Casino)//</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Martes y Jueves en ausencia de Juan Jose</t>
     </r>
   </si>
   <si>
@@ -736,6 +706,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -748,24 +724,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2142,23 +2112,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" s="2" customFormat="1">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="33"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="H2" s="31" t="s">
+      <c r="F2" s="33"/>
+      <c r="H2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="K2" s="31" t="s">
+      <c r="I2" s="33"/>
+      <c r="K2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="31"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B3" s="3" t="s">
@@ -2513,14 +2483,14 @@
       </c>
     </row>
     <row r="17" spans="2:12" s="2" customFormat="1">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="E17" s="31" t="s">
+      <c r="C17" s="33"/>
+      <c r="E17" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="31"/>
+      <c r="F17" s="33"/>
     </row>
     <row r="18" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B18" s="3" t="s">
@@ -2535,14 +2505,14 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="31"/>
-      <c r="K18" s="31" t="s">
+      <c r="I18" s="33"/>
+      <c r="K18" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="31"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="2:12" s="2" customFormat="1" ht="28.95" customHeight="1">
       <c r="B19" s="6" t="s">
@@ -2828,14 +2798,14 @@
       </c>
       <c r="D32"/>
       <c r="F32" s="1"/>
-      <c r="H32" s="32" t="s">
+      <c r="H32" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="33"/>
-      <c r="K32" s="31" t="s">
+      <c r="I32" s="35"/>
+      <c r="K32" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="31"/>
+      <c r="L32" s="33"/>
     </row>
     <row r="33" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B33" s="6" t="s">
@@ -2981,16 +2951,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="101" priority="35"/>
@@ -3142,25 +3112,25 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2"/>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="33"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="33"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="31"/>
+      <c r="I2" s="33"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="31" t="s">
+      <c r="K2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="31"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="2"/>
@@ -3576,10 +3546,10 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2"/>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="31"/>
+      <c r="C17" s="33"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="G17" s="2"/>
@@ -3598,20 +3568,20 @@
         <v>5</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="31"/>
+      <c r="F18" s="33"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="31" t="s">
+      <c r="H18" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="31"/>
+      <c r="I18" s="33"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="31" t="s">
+      <c r="K18" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="31"/>
+      <c r="L18" s="33"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="2"/>
@@ -3839,10 +3809,10 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2"/>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="31"/>
+      <c r="C27" s="33"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="1"/>
@@ -3968,15 +3938,15 @@
       <c r="E32" s="2"/>
       <c r="F32" s="1"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="32" t="s">
+      <c r="H32" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="33"/>
+      <c r="I32" s="35"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="31" t="s">
+      <c r="K32" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="31"/>
+      <c r="L32" s="33"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="2"/>
@@ -4241,40 +4211,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="34"/>
-      <c r="B1" s="34"/>
+      <c r="A1" s="36"/>
+      <c r="B1" s="36"/>
       <c r="C1" s="24"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
       <c r="I1" s="23"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
       <c r="L1" s="23"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="23"/>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="36"/>
+      <c r="C2" s="42"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="36"/>
+      <c r="F2" s="42"/>
       <c r="G2" s="23"/>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="36"/>
+      <c r="I2" s="42"/>
       <c r="J2" s="23"/>
-      <c r="K2" s="35" t="s">
+      <c r="K2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="36"/>
+      <c r="L2" s="42"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="23"/>
@@ -4637,8 +4607,8 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="14.4">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="24"/>
       <c r="D15" s="23"/>
       <c r="E15" s="9" t="s">
@@ -4663,11 +4633,11 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="14.4">
-      <c r="A16" s="34"/>
-      <c r="B16" s="34"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="24"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="19" t="s">
@@ -4686,20 +4656,20 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="23"/>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="36"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="36"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="34"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="23"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
       <c r="L17" s="23"/>
     </row>
     <row r="18" spans="1:12" ht="14.4">
@@ -4718,15 +4688,15 @@
         <v>5</v>
       </c>
       <c r="G18" s="23"/>
-      <c r="H18" s="35" t="s">
+      <c r="H18" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="36"/>
+      <c r="I18" s="42"/>
       <c r="J18" s="23"/>
-      <c r="K18" s="35" t="s">
+      <c r="K18" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="36"/>
+      <c r="L18" s="42"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="23"/>
@@ -4856,8 +4826,8 @@
       <c r="C23" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="34"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="36"/>
       <c r="F23" s="24"/>
       <c r="G23" s="23"/>
       <c r="H23" s="10" t="s">
@@ -4882,8 +4852,8 @@
       <c r="C24" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="34"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="36"/>
       <c r="F24" s="24"/>
       <c r="G24" s="23"/>
       <c r="H24" s="10" t="s">
@@ -4908,8 +4878,8 @@
       <c r="C25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="37"/>
-      <c r="E25" s="34"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="36"/>
       <c r="F25" s="24"/>
       <c r="G25" s="23"/>
       <c r="H25" s="10" t="s">
@@ -4927,11 +4897,11 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="14.4">
-      <c r="A26" s="34"/>
-      <c r="B26" s="34"/>
+      <c r="A26" s="36"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="24"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="24"/>
       <c r="G26" s="23"/>
       <c r="H26" s="10" t="s">
@@ -4950,12 +4920,12 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="23"/>
-      <c r="B27" s="35" t="s">
+      <c r="B27" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="36"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="34"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="36"/>
       <c r="F27" s="24"/>
       <c r="G27" s="23"/>
       <c r="H27" s="10" t="s">
@@ -4980,8 +4950,8 @@
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="37"/>
-      <c r="E28" s="34"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="36"/>
       <c r="F28" s="24"/>
       <c r="G28" s="23"/>
       <c r="H28" s="10" t="s">
@@ -5006,8 +4976,8 @@
       <c r="C29" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="37"/>
-      <c r="E29" s="34"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="36"/>
       <c r="F29" s="24"/>
       <c r="G29" s="23"/>
       <c r="H29" s="10" t="s">
@@ -5032,8 +5002,8 @@
       <c r="C30" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="37"/>
-      <c r="E30" s="34"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="36"/>
       <c r="F30" s="24"/>
       <c r="G30" s="23"/>
       <c r="H30" s="22" t="s">
@@ -5058,14 +5028,14 @@
       <c r="C31" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="37"/>
-      <c r="E31" s="34"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="36"/>
       <c r="F31" s="24"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
       <c r="I31" s="23"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
       <c r="L31" s="23"/>
     </row>
     <row r="32" spans="1:12">
@@ -5076,19 +5046,19 @@
       <c r="C32" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="37"/>
       <c r="F32" s="24"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="35" t="s">
+      <c r="H32" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="40"/>
+      <c r="I32" s="41"/>
       <c r="J32" s="23"/>
-      <c r="K32" s="35" t="s">
+      <c r="K32" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="36"/>
+      <c r="L32" s="42"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="23"/>
@@ -5098,8 +5068,8 @@
       <c r="C33" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="38"/>
-      <c r="E33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="37"/>
       <c r="F33" s="24"/>
       <c r="G33" s="23"/>
       <c r="H33" s="3" t="s">
@@ -5124,8 +5094,8 @@
       <c r="C34" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="38"/>
-      <c r="E34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="37"/>
       <c r="F34" s="24"/>
       <c r="G34" s="23"/>
       <c r="H34" s="9" t="s">
@@ -5150,8 +5120,8 @@
       <c r="C35" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="38"/>
-      <c r="E35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="37"/>
       <c r="F35" s="24"/>
       <c r="G35" s="23"/>
       <c r="H35" s="9" t="s">
@@ -5176,8 +5146,8 @@
       <c r="C36" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="38"/>
-      <c r="E36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="37"/>
       <c r="F36" s="24"/>
       <c r="G36" s="23"/>
       <c r="H36" s="9" t="s">
@@ -5202,8 +5172,8 @@
       <c r="C37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="38"/>
-      <c r="E37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="37"/>
       <c r="F37" s="24"/>
       <c r="G37" s="23"/>
       <c r="H37" s="9" t="s">
@@ -5221,11 +5191,11 @@
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="34"/>
-      <c r="B38" s="34"/>
+      <c r="A38" s="36"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="24"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
       <c r="F38" s="24"/>
       <c r="G38" s="23"/>
       <c r="H38" s="9" t="s">
@@ -5243,49 +5213,89 @@
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="34"/>
-      <c r="B39" s="34"/>
+      <c r="A39" s="36"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
       <c r="F39" s="24"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
       <c r="I39" s="23"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="36"/>
       <c r="L39" s="23"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="34"/>
-      <c r="B40" s="34"/>
+      <c r="A40" s="36"/>
+      <c r="B40" s="36"/>
       <c r="C40" s="24"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
       <c r="F40" s="24"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
       <c r="I40" s="23"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
       <c r="L40" s="23"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="34"/>
-      <c r="B41" s="34"/>
+      <c r="A41" s="36"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="24"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
       <c r="F41" s="24"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
       <c r="I41" s="23"/>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="36"/>
       <c r="L41" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="G41:H41"/>
@@ -5298,53 +5308,13 @@
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="J40:K40"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0797C7-DA66-4603-8F20-80D6408B720F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFACAFD7-E34E-4ED2-9A33-3230CF740C56}">
   <dimension ref="B2:L40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
   <cols>
@@ -5364,23 +5334,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="33"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="31"/>
-      <c r="H2" s="31" t="s">
+      <c r="F2" s="33"/>
+      <c r="H2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="K2" s="31" t="s">
+      <c r="I2" s="33"/>
+      <c r="K2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="31"/>
+      <c r="L2" s="33"/>
     </row>
     <row r="3" spans="2:12" ht="14.4">
       <c r="B3" s="3" t="s">
@@ -5410,8 +5380,8 @@
       </c>
     </row>
     <row r="4" spans="2:12" ht="14.4">
-      <c r="B4" s="4" t="s">
-        <v>7</v>
+      <c r="B4" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>11</v>
@@ -5437,7 +5407,7 @@
     </row>
     <row r="5" spans="2:12" ht="14.4">
       <c r="B5" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>13</v>
@@ -5462,8 +5432,8 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="14.4">
-      <c r="B6" s="6" t="s">
-        <v>9</v>
+      <c r="B6" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>11</v>
@@ -5489,7 +5459,7 @@
     </row>
     <row r="7" spans="2:12" ht="14.4">
       <c r="B7" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>13</v>
@@ -5515,7 +5485,7 @@
     </row>
     <row r="8" spans="2:12" ht="14.4">
       <c r="B8" s="6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>11</v>
@@ -5541,7 +5511,7 @@
     </row>
     <row r="9" spans="2:12" ht="14.4">
       <c r="B9" s="6" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>13</v>
@@ -5567,7 +5537,7 @@
     </row>
     <row r="10" spans="2:12" ht="14.4">
       <c r="B10" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>11</v>
@@ -5592,8 +5562,8 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="14.4">
-      <c r="B11" s="8" t="s">
-        <v>30</v>
+      <c r="B11" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>13</v>
@@ -5619,7 +5589,7 @@
     </row>
     <row r="12" spans="2:12" ht="14.4">
       <c r="B12" s="6" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>11</v>
@@ -5645,7 +5615,7 @@
     </row>
     <row r="13" spans="2:12" ht="14.4">
       <c r="B13" s="8" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>13</v>
@@ -5671,8 +5641,8 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="14.4">
-      <c r="B14" s="8" t="s">
-        <v>104</v>
+      <c r="B14" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>11</v>
@@ -5717,33 +5687,39 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="14.4">
-      <c r="E16" s="6" t="s">
-        <v>44</v>
+    <row r="16" spans="2:12" ht="27.6">
+      <c r="E16" s="19" t="s">
+        <v>103</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>45</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="17" spans="2:12">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="31"/>
+      <c r="C17" s="33"/>
+      <c r="E17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="18" spans="2:12" ht="14.4">
       <c r="B18" s="3" t="s">
@@ -5752,41 +5728,36 @@
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="2:12" ht="14.4">
-      <c r="B19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="31"/>
-      <c r="H19" s="31" t="s">
+      <c r="E18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="27.6">
+      <c r="B19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="E19" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="31"/>
-      <c r="K19" s="31" t="s">
+      <c r="I19" s="33"/>
+      <c r="K19" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="L19" s="31"/>
+      <c r="L19" s="33"/>
     </row>
     <row r="20" spans="2:12" ht="14.4">
-      <c r="B20" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="32"/>
       <c r="H20" s="3" t="s">
         <v>6</v>
       </c>
@@ -5801,18 +5772,7 @@
       </c>
     </row>
     <row r="21" spans="2:12" ht="14.4">
-      <c r="B21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="F21" s="2"/>
       <c r="H21" s="12" t="s">
         <v>96</v>
       </c>
@@ -5827,18 +5787,14 @@
       </c>
     </row>
     <row r="22" spans="2:12" ht="14.4">
-      <c r="B22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="B22" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="33"/>
+      <c r="E22" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="33"/>
       <c r="H22" s="12" t="s">
         <v>16</v>
       </c>
@@ -5853,17 +5809,17 @@
       </c>
     </row>
     <row r="23" spans="2:12" ht="14.4">
-      <c r="B23" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>40</v>
+      <c r="B23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>97</v>
@@ -5878,15 +5834,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="27.6">
+    <row r="24" spans="2:12" ht="14.4">
       <c r="B24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>40</v>
@@ -5905,11 +5861,17 @@
       </c>
     </row>
     <row r="25" spans="2:12" ht="14.4">
-      <c r="B25" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>33</v>
+      <c r="B25" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>20</v>
@@ -5926,10 +5888,16 @@
     </row>
     <row r="26" spans="2:12" ht="14.4">
       <c r="B26" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>33</v>
+        <v>79</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>98</v>
@@ -5945,8 +5913,18 @@
       </c>
     </row>
     <row r="27" spans="2:12" ht="14.4">
-      <c r="B27" s="41"/>
-      <c r="C27" s="42"/>
+      <c r="B27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="H27" s="12" t="s">
         <v>17</v>
       </c>
@@ -5961,6 +5939,18 @@
       </c>
     </row>
     <row r="28" spans="2:12" ht="14.4">
+      <c r="B28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="H28" s="12" t="s">
         <v>23</v>
       </c>
@@ -5975,10 +5965,12 @@
       </c>
     </row>
     <row r="29" spans="2:12" ht="14.4">
-      <c r="B29" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="31"/>
+      <c r="B29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="H29" s="12" t="s">
         <v>22</v>
       </c>
@@ -5993,11 +5985,11 @@
       </c>
     </row>
     <row r="30" spans="2:12" ht="14.4">
-      <c r="B30" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>5</v>
+      <c r="B30" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>99</v>
@@ -6013,11 +6005,11 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="14.4">
-      <c r="B31" s="8" t="s">
-        <v>27</v>
+      <c r="B31" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>79</v>
@@ -6034,60 +6026,48 @@
       </c>
     </row>
     <row r="32" spans="2:12" ht="14.4">
-      <c r="B32" s="17" t="s">
-        <v>35</v>
+      <c r="B32" s="19" t="s">
+        <v>103</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D32"/>
       <c r="H32" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>13</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="33" spans="2:12">
-      <c r="B33" s="8" t="s">
-        <v>79</v>
+      <c r="B33" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D33"/>
     </row>
     <row r="34" spans="2:12">
-      <c r="B34" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="D34"/>
-      <c r="H34" s="32" t="s">
+      <c r="H34" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I34" s="33"/>
-      <c r="K34" s="31" t="s">
+      <c r="I34" s="35"/>
+      <c r="K34" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="L34" s="31"/>
+      <c r="L34" s="33"/>
     </row>
     <row r="35" spans="2:12" ht="14.4">
-      <c r="B35" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="D35"/>
       <c r="H35" s="3" t="s">
         <v>39</v>
@@ -6103,12 +6083,6 @@
       </c>
     </row>
     <row r="36" spans="2:12">
-      <c r="B36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="D36"/>
       <c r="H36" s="6" t="s">
         <v>12</v>
@@ -6124,12 +6098,6 @@
       </c>
     </row>
     <row r="37" spans="2:12">
-      <c r="B37" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="D37"/>
       <c r="H37" s="6" t="s">
         <v>16</v>
@@ -6145,12 +6113,6 @@
       </c>
     </row>
     <row r="38" spans="2:12">
-      <c r="B38" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>43</v>
@@ -6166,12 +6128,6 @@
       </c>
     </row>
     <row r="39" spans="2:12">
-      <c r="B39" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>22</v>
@@ -6201,42 +6157,41 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="EuO9at0TXMwgajATRRwMQok4w72EQ4ahdYJ+6J3w7mQdEsRr6kNEB9B6jgIce5y+0FTqsYhoMaaQ6QUsEJuxHA==" saltValue="TM0jAjYbq8HFQYXEp7A2hQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="K34:L34"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E19:F19"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="K19:L19"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6">
+  <conditionalFormatting sqref="B8">
     <cfRule type="duplicateValues" dxfId="34" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7">
+  <conditionalFormatting sqref="B9">
     <cfRule type="duplicateValues" dxfId="33" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8">
+  <conditionalFormatting sqref="B10">
     <cfRule type="duplicateValues" dxfId="32" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B36 B9">
-    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12 B15">
-    <cfRule type="duplicateValues" dxfId="30" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B33 B25:B27">
-    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34 B10">
-    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37 B31 B11">
+  <conditionalFormatting sqref="B14:B15">
+    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26 B20 E18:E19">
+    <cfRule type="duplicateValues" dxfId="30" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27 B12">
+    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28:B29 B11">
+    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30 B24 B13">
     <cfRule type="duplicateValues" dxfId="27" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
@@ -6260,10 +6215,10 @@
   <conditionalFormatting sqref="E14">
     <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15 E17">
+  <conditionalFormatting sqref="E20 E15">
     <cfRule type="duplicateValues" dxfId="19" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E24">
+  <conditionalFormatting sqref="E27">
     <cfRule type="duplicateValues" dxfId="18" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
@@ -6549,6 +6504,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -6749,12 +6710,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
@@ -6764,6 +6719,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6780,13 +6744,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD4589F-0177-494E-BD95-9C38BE377AF0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953B1AF5-A04A-42A8-898C-405712CB1D03}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
     <sheet name="Semana 2 - 7 Sep al 13 Sep" sheetId="9" r:id="rId2"/>
     <sheet name="Semana 3 - 14 al 20 Sep" sheetId="15" r:id="rId3"/>
-    <sheet name="Semana 4 - 21 al 27 Sep" sheetId="20" r:id="rId4"/>
+    <sheet name="Semana 4 - 21 al 27 Sep" sheetId="21" r:id="rId4"/>
     <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="105">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -724,18 +724,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2951,16 +2951,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="101" priority="35"/>
@@ -4226,25 +4226,25 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="23"/>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="42"/>
+      <c r="F2" s="38"/>
       <c r="G2" s="23"/>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="42"/>
+      <c r="I2" s="38"/>
       <c r="J2" s="23"/>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="42"/>
+      <c r="L2" s="38"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="23"/>
@@ -4656,16 +4656,16 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="23"/>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="42"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
       <c r="H17" s="36"/>
       <c r="I17" s="23"/>
       <c r="J17" s="36"/>
@@ -4688,15 +4688,15 @@
         <v>5</v>
       </c>
       <c r="G18" s="23"/>
-      <c r="H18" s="40" t="s">
+      <c r="H18" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="42"/>
+      <c r="I18" s="38"/>
       <c r="J18" s="23"/>
-      <c r="K18" s="40" t="s">
+      <c r="K18" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="42"/>
+      <c r="L18" s="38"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="23"/>
@@ -4826,7 +4826,7 @@
       <c r="C23" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="38"/>
+      <c r="D23" s="39"/>
       <c r="E23" s="36"/>
       <c r="F23" s="24"/>
       <c r="G23" s="23"/>
@@ -4852,7 +4852,7 @@
       <c r="C24" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="38"/>
+      <c r="D24" s="39"/>
       <c r="E24" s="36"/>
       <c r="F24" s="24"/>
       <c r="G24" s="23"/>
@@ -4878,7 +4878,7 @@
       <c r="C25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="38"/>
+      <c r="D25" s="39"/>
       <c r="E25" s="36"/>
       <c r="F25" s="24"/>
       <c r="G25" s="23"/>
@@ -4920,11 +4920,11 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="23"/>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="39"/>
       <c r="E27" s="36"/>
       <c r="F27" s="24"/>
       <c r="G27" s="23"/>
@@ -4950,7 +4950,7 @@
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="38"/>
+      <c r="D28" s="39"/>
       <c r="E28" s="36"/>
       <c r="F28" s="24"/>
       <c r="G28" s="23"/>
@@ -4976,7 +4976,7 @@
       <c r="C29" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="38"/>
+      <c r="D29" s="39"/>
       <c r="E29" s="36"/>
       <c r="F29" s="24"/>
       <c r="G29" s="23"/>
@@ -5002,7 +5002,7 @@
       <c r="C30" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="38"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="36"/>
       <c r="F30" s="24"/>
       <c r="G30" s="23"/>
@@ -5028,7 +5028,7 @@
       <c r="C31" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="38"/>
+      <c r="D31" s="39"/>
       <c r="E31" s="36"/>
       <c r="F31" s="24"/>
       <c r="G31" s="36"/>
@@ -5046,19 +5046,19 @@
       <c r="C32" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="37"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="41"/>
       <c r="F32" s="24"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="40" t="s">
+      <c r="H32" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="41"/>
+      <c r="I32" s="42"/>
       <c r="J32" s="23"/>
-      <c r="K32" s="40" t="s">
+      <c r="K32" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="42"/>
+      <c r="L32" s="38"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="23"/>
@@ -5068,8 +5068,8 @@
       <c r="C33" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="37"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="41"/>
       <c r="F33" s="24"/>
       <c r="G33" s="23"/>
       <c r="H33" s="3" t="s">
@@ -5094,8 +5094,8 @@
       <c r="C34" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="37"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="41"/>
       <c r="F34" s="24"/>
       <c r="G34" s="23"/>
       <c r="H34" s="9" t="s">
@@ -5120,8 +5120,8 @@
       <c r="C35" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="37"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="41"/>
       <c r="F35" s="24"/>
       <c r="G35" s="23"/>
       <c r="H35" s="9" t="s">
@@ -5146,8 +5146,8 @@
       <c r="C36" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="37"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="41"/>
       <c r="F36" s="24"/>
       <c r="G36" s="23"/>
       <c r="H36" s="9" t="s">
@@ -5172,8 +5172,8 @@
       <c r="C37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="37"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="41"/>
       <c r="F37" s="24"/>
       <c r="G37" s="23"/>
       <c r="H37" s="9" t="s">
@@ -5194,8 +5194,8 @@
       <c r="A38" s="36"/>
       <c r="B38" s="36"/>
       <c r="C38" s="24"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
       <c r="F38" s="24"/>
       <c r="G38" s="23"/>
       <c r="H38" s="9" t="s">
@@ -5216,8 +5216,8 @@
       <c r="A39" s="36"/>
       <c r="B39" s="36"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
       <c r="F39" s="24"/>
       <c r="G39" s="36"/>
       <c r="H39" s="36"/>
@@ -5230,8 +5230,8 @@
       <c r="A40" s="36"/>
       <c r="B40" s="36"/>
       <c r="C40" s="24"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
       <c r="F40" s="24"/>
       <c r="G40" s="36"/>
       <c r="H40" s="36"/>
@@ -5244,8 +5244,8 @@
       <c r="A41" s="36"/>
       <c r="B41" s="36"/>
       <c r="C41" s="24"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
       <c r="F41" s="24"/>
       <c r="G41" s="36"/>
       <c r="H41" s="36"/>
@@ -5256,46 +5256,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="G41:H41"/>
@@ -5308,22 +5268,62 @@
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="J40:K40"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFACAFD7-E34E-4ED2-9A33-3230CF740C56}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6268B87-F97A-4AF4-A331-D1B79ABD8A13}">
   <dimension ref="B2:L40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="3.3984375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="93.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="76.69921875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.3984375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="52.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="61.8984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.59765625" style="2" customWidth="1"/>
     <col min="8" max="8" width="61.8984375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.69921875" style="2" customWidth="1"/>
@@ -5668,6 +5668,12 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="14.4">
+      <c r="B15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="E15" s="6" t="s">
         <v>36</v>
       </c>
@@ -5687,7 +5693,13 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="27.6">
+    <row r="16" spans="2:12" ht="14.4">
+      <c r="B16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="E16" s="19" t="s">
         <v>103</v>
       </c>
@@ -5710,10 +5722,12 @@
       </c>
     </row>
     <row r="17" spans="2:12">
-      <c r="B17" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="33"/>
+      <c r="B17" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="E17" s="6" t="s">
         <v>26</v>
       </c>
@@ -5721,13 +5735,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="14.4">
-      <c r="B18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>5</v>
-      </c>
+    <row r="18" spans="2:12">
       <c r="E18" s="8" t="s">
         <v>34</v>
       </c>
@@ -5735,11 +5743,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="27.6">
-      <c r="B19" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="7"/>
+    <row r="19" spans="2:12">
+      <c r="B19" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="33"/>
       <c r="E19" s="8" t="s">
         <v>104</v>
       </c>
@@ -5756,8 +5764,18 @@
       <c r="L19" s="33"/>
     </row>
     <row r="20" spans="2:12" ht="14.4">
-      <c r="B20" s="31"/>
-      <c r="C20" s="32"/>
+      <c r="B20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="H20" s="3" t="s">
         <v>6</v>
       </c>
@@ -5771,8 +5789,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="14.4">
-      <c r="F21" s="2"/>
+    <row r="21" spans="2:12" ht="27.6">
+      <c r="B21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="E21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="H21" s="12" t="s">
         <v>96</v>
       </c>
@@ -5787,14 +5814,14 @@
       </c>
     </row>
     <row r="22" spans="2:12" ht="14.4">
-      <c r="B22" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="33"/>
-      <c r="E22" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="33"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
+      <c r="E22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="H22" s="12" t="s">
         <v>16</v>
       </c>
@@ -5809,17 +5836,11 @@
       </c>
     </row>
     <row r="23" spans="2:12" ht="14.4">
-      <c r="B23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>5</v>
+      <c r="E23" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>97</v>
@@ -5835,18 +5856,6 @@
       </c>
     </row>
     <row r="24" spans="2:12" ht="14.4">
-      <c r="B24" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="H24" s="12" t="s">
         <v>7</v>
       </c>
@@ -5861,18 +5870,7 @@
       </c>
     </row>
     <row r="25" spans="2:12" ht="14.4">
-      <c r="B25" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="F25" s="2"/>
       <c r="H25" s="12" t="s">
         <v>20</v>
       </c>
@@ -5887,18 +5885,10 @@
       </c>
     </row>
     <row r="26" spans="2:12" ht="14.4">
-      <c r="B26" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>40</v>
-      </c>
+      <c r="E26" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="33"/>
       <c r="H26" s="12" t="s">
         <v>98</v>
       </c>
@@ -5913,17 +5903,11 @@
       </c>
     </row>
     <row r="27" spans="2:12" ht="14.4">
-      <c r="B27" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>40</v>
+      <c r="E27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>17</v>
@@ -5939,14 +5923,8 @@
       </c>
     </row>
     <row r="28" spans="2:12" ht="14.4">
-      <c r="B28" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>18</v>
+      <c r="E28" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>40</v>
@@ -5965,11 +5943,11 @@
       </c>
     </row>
     <row r="29" spans="2:12" ht="14.4">
-      <c r="B29" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>8</v>
+      <c r="E29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>22</v>
@@ -5985,11 +5963,11 @@
       </c>
     </row>
     <row r="30" spans="2:12" ht="14.4">
-      <c r="B30" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>8</v>
+      <c r="E30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>99</v>
@@ -6005,11 +5983,11 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="14.4">
-      <c r="B31" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>8</v>
+      <c r="E31" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>79</v>
@@ -6026,13 +6004,13 @@
       </c>
     </row>
     <row r="32" spans="2:12" ht="14.4">
-      <c r="B32" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="D32"/>
+      <c r="E32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="H32" s="19" t="s">
         <v>103</v>
       </c>
@@ -6047,16 +6025,10 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="2:12">
-      <c r="B33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>8</v>
-      </c>
+    <row r="33" spans="4:12">
       <c r="D33"/>
     </row>
-    <row r="34" spans="2:12">
+    <row r="34" spans="4:12">
       <c r="D34"/>
       <c r="H34" s="34" t="s">
         <v>46</v>
@@ -6067,7 +6039,7 @@
       </c>
       <c r="L34" s="33"/>
     </row>
-    <row r="35" spans="2:12" ht="14.4">
+    <row r="35" spans="4:12" ht="14.4">
       <c r="D35"/>
       <c r="H35" s="3" t="s">
         <v>39</v>
@@ -6082,7 +6054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="2:12">
+    <row r="36" spans="4:12">
       <c r="D36"/>
       <c r="H36" s="6" t="s">
         <v>12</v>
@@ -6097,7 +6069,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="2:12">
+    <row r="37" spans="4:12">
       <c r="D37"/>
       <c r="H37" s="6" t="s">
         <v>16</v>
@@ -6112,7 +6084,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="2:12">
+    <row r="38" spans="4:12">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>43</v>
@@ -6127,7 +6099,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="2:12">
+    <row r="39" spans="4:12">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>22</v>
@@ -6142,7 +6114,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="2:12">
+    <row r="40" spans="4:12">
       <c r="H40" s="6" t="s">
         <v>21</v>
       </c>
@@ -6157,16 +6129,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B22:C22"/>
+  <mergeCells count="10">
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="K34:L34"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="K19:L19"/>
   </mergeCells>
@@ -6179,101 +6150,101 @@
   <conditionalFormatting sqref="B10">
     <cfRule type="duplicateValues" dxfId="32" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:B15">
-    <cfRule type="duplicateValues" dxfId="31" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26 B20 E18:E19">
-    <cfRule type="duplicateValues" dxfId="30" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27 B12">
-    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B28:B29 B11">
-    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B30 B24 B13">
-    <cfRule type="duplicateValues" dxfId="27" priority="33"/>
+  <conditionalFormatting sqref="B22 E23 E18:E19">
+    <cfRule type="duplicateValues" dxfId="31" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12 B16">
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="26" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="24" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="23" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="22" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E20 E15">
-    <cfRule type="duplicateValues" dxfId="19" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E27">
-    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24 E15">
+    <cfRule type="duplicateValues" dxfId="22" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E31">
+    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="14" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="10" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="3" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11 E20">
+    <cfRule type="duplicateValues" dxfId="2" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E21 B13">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6495,21 +6466,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -6710,24 +6666,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6744,4 +6698,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953B1AF5-A04A-42A8-898C-405712CB1D03}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E4E51E-5191-4E76-B08C-9005598E91BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
     <sheet name="Semana 2 - 7 Sep al 13 Sep" sheetId="9" r:id="rId2"/>
     <sheet name="Semana 3 - 14 al 20 Sep" sheetId="15" r:id="rId3"/>
-    <sheet name="Semana 4 - 21 al 27 Sep" sheetId="21" r:id="rId4"/>
+    <sheet name="Semana 4 - 21 al 27 Sep" sheetId="22" r:id="rId4"/>
     <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="107">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -404,6 +404,12 @@
   </si>
   <si>
     <t>Revisión RiskLive (Usuarios que cruzaron en Pragmatic)</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>Aprobación de retiros Punto de Venta y Tranferencia (Los partner con mas retiros pendientes)</t>
   </si>
 </sst>
 </file>
@@ -724,18 +730,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2951,16 +2957,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
     <cfRule type="duplicateValues" dxfId="101" priority="35"/>
@@ -4226,25 +4232,25 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="23"/>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="38"/>
+      <c r="C2" s="42"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="38"/>
+      <c r="F2" s="42"/>
       <c r="G2" s="23"/>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="38"/>
+      <c r="I2" s="42"/>
       <c r="J2" s="23"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="38"/>
+      <c r="L2" s="42"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="23"/>
@@ -4656,16 +4662,16 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="23"/>
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="38"/>
+      <c r="C17" s="42"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="38"/>
-      <c r="G17" s="39"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="38"/>
       <c r="H17" s="36"/>
       <c r="I17" s="23"/>
       <c r="J17" s="36"/>
@@ -4688,15 +4694,15 @@
         <v>5</v>
       </c>
       <c r="G18" s="23"/>
-      <c r="H18" s="37" t="s">
+      <c r="H18" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="38"/>
+      <c r="I18" s="42"/>
       <c r="J18" s="23"/>
-      <c r="K18" s="37" t="s">
+      <c r="K18" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="38"/>
+      <c r="L18" s="42"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="23"/>
@@ -4826,7 +4832,7 @@
       <c r="C23" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="39"/>
+      <c r="D23" s="38"/>
       <c r="E23" s="36"/>
       <c r="F23" s="24"/>
       <c r="G23" s="23"/>
@@ -4852,7 +4858,7 @@
       <c r="C24" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="39"/>
+      <c r="D24" s="38"/>
       <c r="E24" s="36"/>
       <c r="F24" s="24"/>
       <c r="G24" s="23"/>
@@ -4878,7 +4884,7 @@
       <c r="C25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="39"/>
+      <c r="D25" s="38"/>
       <c r="E25" s="36"/>
       <c r="F25" s="24"/>
       <c r="G25" s="23"/>
@@ -4920,11 +4926,11 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="23"/>
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="38"/>
-      <c r="D27" s="39"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="38"/>
       <c r="E27" s="36"/>
       <c r="F27" s="24"/>
       <c r="G27" s="23"/>
@@ -4950,7 +4956,7 @@
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="39"/>
+      <c r="D28" s="38"/>
       <c r="E28" s="36"/>
       <c r="F28" s="24"/>
       <c r="G28" s="23"/>
@@ -4976,7 +4982,7 @@
       <c r="C29" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="39"/>
+      <c r="D29" s="38"/>
       <c r="E29" s="36"/>
       <c r="F29" s="24"/>
       <c r="G29" s="23"/>
@@ -5002,7 +5008,7 @@
       <c r="C30" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="39"/>
+      <c r="D30" s="38"/>
       <c r="E30" s="36"/>
       <c r="F30" s="24"/>
       <c r="G30" s="23"/>
@@ -5028,7 +5034,7 @@
       <c r="C31" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="39"/>
+      <c r="D31" s="38"/>
       <c r="E31" s="36"/>
       <c r="F31" s="24"/>
       <c r="G31" s="36"/>
@@ -5046,19 +5052,19 @@
       <c r="C32" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="40"/>
-      <c r="E32" s="41"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="37"/>
       <c r="F32" s="24"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="37" t="s">
+      <c r="H32" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="42"/>
+      <c r="I32" s="41"/>
       <c r="J32" s="23"/>
-      <c r="K32" s="37" t="s">
+      <c r="K32" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="38"/>
+      <c r="L32" s="42"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="23"/>
@@ -5068,8 +5074,8 @@
       <c r="C33" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="37"/>
       <c r="F33" s="24"/>
       <c r="G33" s="23"/>
       <c r="H33" s="3" t="s">
@@ -5094,8 +5100,8 @@
       <c r="C34" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="40"/>
-      <c r="E34" s="41"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="37"/>
       <c r="F34" s="24"/>
       <c r="G34" s="23"/>
       <c r="H34" s="9" t="s">
@@ -5120,8 +5126,8 @@
       <c r="C35" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="40"/>
-      <c r="E35" s="41"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="37"/>
       <c r="F35" s="24"/>
       <c r="G35" s="23"/>
       <c r="H35" s="9" t="s">
@@ -5146,8 +5152,8 @@
       <c r="C36" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="40"/>
-      <c r="E36" s="41"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="37"/>
       <c r="F36" s="24"/>
       <c r="G36" s="23"/>
       <c r="H36" s="9" t="s">
@@ -5172,8 +5178,8 @@
       <c r="C37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="40"/>
-      <c r="E37" s="41"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="37"/>
       <c r="F37" s="24"/>
       <c r="G37" s="23"/>
       <c r="H37" s="9" t="s">
@@ -5194,8 +5200,8 @@
       <c r="A38" s="36"/>
       <c r="B38" s="36"/>
       <c r="C38" s="24"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
       <c r="F38" s="24"/>
       <c r="G38" s="23"/>
       <c r="H38" s="9" t="s">
@@ -5216,8 +5222,8 @@
       <c r="A39" s="36"/>
       <c r="B39" s="36"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
       <c r="F39" s="24"/>
       <c r="G39" s="36"/>
       <c r="H39" s="36"/>
@@ -5230,8 +5236,8 @@
       <c r="A40" s="36"/>
       <c r="B40" s="36"/>
       <c r="C40" s="24"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
       <c r="F40" s="24"/>
       <c r="G40" s="36"/>
       <c r="H40" s="36"/>
@@ -5244,8 +5250,8 @@
       <c r="A41" s="36"/>
       <c r="B41" s="36"/>
       <c r="C41" s="24"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="41"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
       <c r="F41" s="24"/>
       <c r="G41" s="36"/>
       <c r="H41" s="36"/>
@@ -5256,6 +5262,46 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="G41:H41"/>
@@ -5268,69 +5314,29 @@
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="J40:K40"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6268B87-F97A-4AF4-A331-D1B79ABD8A13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DAFF9F4-2F49-4782-8DB6-B00572BA11C0}">
   <dimension ref="B2:L40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="3.3984375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="76.69921875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="93.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.3984375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="61.8984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.59765625" style="2" customWidth="1"/>
     <col min="8" max="8" width="61.8984375" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.69921875" style="2" customWidth="1"/>
     <col min="10" max="10" width="5.59765625" style="2" customWidth="1"/>
     <col min="11" max="11" width="61.8984375" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.69921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.59765625" style="2"/>
+    <col min="13" max="16384" width="11.3984375" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12">
@@ -5668,12 +5674,6 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="14.4">
-      <c r="B15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="E15" s="6" t="s">
         <v>36</v>
       </c>
@@ -5693,13 +5693,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="14.4">
-      <c r="B16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>11</v>
-      </c>
+    <row r="16" spans="2:12" ht="27.6">
       <c r="E16" s="19" t="s">
         <v>103</v>
       </c>
@@ -5722,12 +5716,10 @@
       </c>
     </row>
     <row r="17" spans="2:12">
-      <c r="B17" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="B17" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="33"/>
       <c r="E17" s="6" t="s">
         <v>26</v>
       </c>
@@ -5735,7 +5727,13 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="2:12" ht="14.4">
+      <c r="B18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="E18" s="8" t="s">
         <v>34</v>
       </c>
@@ -5743,11 +5741,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="2:12">
-      <c r="B19" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="33"/>
+    <row r="19" spans="2:12" ht="27.6">
+      <c r="B19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="7"/>
       <c r="E19" s="8" t="s">
         <v>104</v>
       </c>
@@ -5764,18 +5762,8 @@
       <c r="L19" s="33"/>
     </row>
     <row r="20" spans="2:12" ht="14.4">
-      <c r="B20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="32"/>
       <c r="H20" s="3" t="s">
         <v>6</v>
       </c>
@@ -5789,17 +5777,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="27.6">
-      <c r="B21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="E21" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>14</v>
-      </c>
+    <row r="21" spans="2:12" ht="14.4">
+      <c r="F21" s="2"/>
       <c r="H21" s="12" t="s">
         <v>96</v>
       </c>
@@ -5814,14 +5793,14 @@
       </c>
     </row>
     <row r="22" spans="2:12" ht="14.4">
-      <c r="B22" s="31"/>
-      <c r="C22" s="32"/>
-      <c r="E22" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="B22" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="33"/>
+      <c r="E22" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="33"/>
       <c r="H22" s="12" t="s">
         <v>16</v>
       </c>
@@ -5836,11 +5815,17 @@
       </c>
     </row>
     <row r="23" spans="2:12" ht="14.4">
-      <c r="E23" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>14</v>
+      <c r="B23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>97</v>
@@ -5856,6 +5841,18 @@
       </c>
     </row>
     <row r="24" spans="2:12" ht="14.4">
+      <c r="B24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="H24" s="12" t="s">
         <v>7</v>
       </c>
@@ -5870,7 +5867,18 @@
       </c>
     </row>
     <row r="25" spans="2:12" ht="14.4">
-      <c r="F25" s="2"/>
+      <c r="B25" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="H25" s="12" t="s">
         <v>20</v>
       </c>
@@ -5885,10 +5893,18 @@
       </c>
     </row>
     <row r="26" spans="2:12" ht="14.4">
-      <c r="E26" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" s="33"/>
+      <c r="B26" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="H26" s="12" t="s">
         <v>98</v>
       </c>
@@ -5903,11 +5919,17 @@
       </c>
     </row>
     <row r="27" spans="2:12" ht="14.4">
-      <c r="E27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>5</v>
+      <c r="B27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>17</v>
@@ -5923,8 +5945,14 @@
       </c>
     </row>
     <row r="28" spans="2:12" ht="14.4">
-      <c r="E28" s="6" t="s">
-        <v>12</v>
+      <c r="B28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>40</v>
@@ -5943,11 +5971,11 @@
       </c>
     </row>
     <row r="29" spans="2:12" ht="14.4">
-      <c r="E29" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>40</v>
+      <c r="B29" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>22</v>
@@ -5963,11 +5991,11 @@
       </c>
     </row>
     <row r="30" spans="2:12" ht="14.4">
-      <c r="E30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>40</v>
+      <c r="B30" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>99</v>
@@ -5983,11 +6011,11 @@
       </c>
     </row>
     <row r="31" spans="2:12" ht="14.4">
-      <c r="E31" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>40</v>
+      <c r="B31" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>79</v>
@@ -6004,13 +6032,11 @@
       </c>
     </row>
     <row r="32" spans="2:12" ht="14.4">
+      <c r="B32" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="5"/>
       <c r="D32"/>
-      <c r="E32" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="H32" s="19" t="s">
         <v>103</v>
       </c>
@@ -6025,10 +6051,14 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="4:12">
+    <row r="33" spans="2:12">
+      <c r="B33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="5"/>
       <c r="D33"/>
     </row>
-    <row r="34" spans="4:12">
+    <row r="34" spans="2:12">
       <c r="D34"/>
       <c r="H34" s="34" t="s">
         <v>46</v>
@@ -6039,7 +6069,7 @@
       </c>
       <c r="L34" s="33"/>
     </row>
-    <row r="35" spans="4:12" ht="14.4">
+    <row r="35" spans="2:12" ht="14.4">
       <c r="D35"/>
       <c r="H35" s="3" t="s">
         <v>39</v>
@@ -6054,7 +6084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="4:12">
+    <row r="36" spans="2:12">
       <c r="D36"/>
       <c r="H36" s="6" t="s">
         <v>12</v>
@@ -6069,7 +6099,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="4:12">
+    <row r="37" spans="2:12">
       <c r="D37"/>
       <c r="H37" s="6" t="s">
         <v>16</v>
@@ -6084,7 +6114,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="4:12">
+    <row r="38" spans="2:12">
       <c r="D38"/>
       <c r="H38" s="6" t="s">
         <v>43</v>
@@ -6099,7 +6129,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="4:12">
+    <row r="39" spans="2:12">
       <c r="D39"/>
       <c r="H39" s="6" t="s">
         <v>22</v>
@@ -6114,7 +6144,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="4:12">
+    <row r="40" spans="2:12">
       <c r="H40" s="6" t="s">
         <v>21</v>
       </c>
@@ -6129,15 +6159,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="E26:F26"/>
+  <mergeCells count="11">
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="K34:L34"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B19:C19"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="K19:L19"/>
   </mergeCells>
@@ -6150,100 +6181,100 @@
   <conditionalFormatting sqref="B10">
     <cfRule type="duplicateValues" dxfId="32" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B22 E23 E18:E19">
-    <cfRule type="duplicateValues" dxfId="31" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12 B16">
-    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
+  <conditionalFormatting sqref="B14:B15">
+    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26 B20 E18:E19">
+    <cfRule type="duplicateValues" dxfId="30" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27 B12">
+    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B24 B13">
+    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="29" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="27" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="26" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="23" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24 E15">
-    <cfRule type="duplicateValues" dxfId="22" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E31">
-    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20 E15">
+    <cfRule type="duplicateValues" dxfId="20" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27">
+    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="16" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="12" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="10" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="3" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11 E20">
-    <cfRule type="duplicateValues" dxfId="2" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E21 B13">
+    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11 B28">
     <cfRule type="duplicateValues" dxfId="0" priority="35"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6466,6 +6497,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -6666,12 +6703,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6682,6 +6713,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6700,15 +6740,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>

--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E4E51E-5191-4E76-B08C-9005598E91BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C30F47-BAE2-4BD8-BE52-84D4ED766983}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
     <sheet name="Semana 2 - 7 Sep al 13 Sep" sheetId="9" r:id="rId2"/>
     <sheet name="Semana 3 - 14 al 20 Sep" sheetId="15" r:id="rId3"/>
     <sheet name="Semana 4 - 21 al 27 Sep" sheetId="22" r:id="rId4"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
+    <sheet name="Semana 5 - 28 Sep al 30 Sep" sheetId="23" r:id="rId5"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="109">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -410,6 +411,36 @@
   </si>
   <si>
     <t>Aprobación de retiros Punto de Venta y Tranferencia (Los partner con mas retiros pendientes)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Apoyo Deltas (Registros, Bonos, Premios Bonos y Bonos Casino)// </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lunes, Martes, Miercoles todo el turno y Jueves en ausencia de Juan Jose</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Apoyo Revisión GGR negativo casino / deportivo// </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lunes, Martes, Miercoles todo el turno y Jueves en ausencia de Juan Jose</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -730,25 +761,215 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="102">
+  <dxfs count="121">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2957,130 +3178,130 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="H18:I18"/>
     <mergeCell ref="K18:L18"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="K32:L32"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="101" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="100" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="99" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="98" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B31">
-    <cfRule type="duplicateValues" dxfId="97" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="96" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B34 B9">
-    <cfRule type="duplicateValues" dxfId="95" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B29 B11">
-    <cfRule type="duplicateValues" dxfId="94" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="93" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="92" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="91" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="90" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="89" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="88" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="87" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="86" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="duplicateValues" dxfId="85" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="84" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="83" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="82" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="81" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="80" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="duplicateValues" dxfId="79" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H26">
-    <cfRule type="duplicateValues" dxfId="78" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="duplicateValues" dxfId="77" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="duplicateValues" dxfId="76" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="75" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="74" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="73" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="72" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="71" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="70" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="69" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="68" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="67" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="duplicateValues" dxfId="66" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="duplicateValues" dxfId="65" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="duplicateValues" dxfId="64" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="23"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4107,91 +4328,91 @@
     <mergeCell ref="K18:L18"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="63" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="62" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="61" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12 B15">
-    <cfRule type="duplicateValues" dxfId="60" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B31">
-    <cfRule type="duplicateValues" dxfId="59" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="58" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="57" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34 B29 B11">
-    <cfRule type="duplicateValues" dxfId="56" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="55" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="54" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="53" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="52" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="51" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="50" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="49" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="48" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23">
-    <cfRule type="duplicateValues" dxfId="47" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="duplicateValues" dxfId="46" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="45" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="44" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="43" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="42" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="41" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="40" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24">
-    <cfRule type="duplicateValues" dxfId="39" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K26">
-    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="duplicateValues" dxfId="37" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="duplicateValues" dxfId="36" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="duplicateValues" dxfId="35" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4232,25 +4453,25 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="23"/>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="42"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="42"/>
+      <c r="F2" s="38"/>
       <c r="G2" s="23"/>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="42"/>
+      <c r="I2" s="38"/>
       <c r="J2" s="23"/>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="42"/>
+      <c r="L2" s="38"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="23"/>
@@ -4662,16 +4883,16 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="23"/>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="42"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="40" t="s">
+      <c r="E17" s="37" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="39"/>
       <c r="H17" s="36"/>
       <c r="I17" s="23"/>
       <c r="J17" s="36"/>
@@ -4694,15 +4915,15 @@
         <v>5</v>
       </c>
       <c r="G18" s="23"/>
-      <c r="H18" s="40" t="s">
+      <c r="H18" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="42"/>
+      <c r="I18" s="38"/>
       <c r="J18" s="23"/>
-      <c r="K18" s="40" t="s">
+      <c r="K18" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="42"/>
+      <c r="L18" s="38"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="23"/>
@@ -4832,7 +5053,7 @@
       <c r="C23" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="38"/>
+      <c r="D23" s="39"/>
       <c r="E23" s="36"/>
       <c r="F23" s="24"/>
       <c r="G23" s="23"/>
@@ -4858,7 +5079,7 @@
       <c r="C24" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="38"/>
+      <c r="D24" s="39"/>
       <c r="E24" s="36"/>
       <c r="F24" s="24"/>
       <c r="G24" s="23"/>
@@ -4884,7 +5105,7 @@
       <c r="C25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="38"/>
+      <c r="D25" s="39"/>
       <c r="E25" s="36"/>
       <c r="F25" s="24"/>
       <c r="G25" s="23"/>
@@ -4926,11 +5147,11 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="23"/>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="42"/>
-      <c r="D27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="39"/>
       <c r="E27" s="36"/>
       <c r="F27" s="24"/>
       <c r="G27" s="23"/>
@@ -4956,7 +5177,7 @@
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="38"/>
+      <c r="D28" s="39"/>
       <c r="E28" s="36"/>
       <c r="F28" s="24"/>
       <c r="G28" s="23"/>
@@ -4982,7 +5203,7 @@
       <c r="C29" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="38"/>
+      <c r="D29" s="39"/>
       <c r="E29" s="36"/>
       <c r="F29" s="24"/>
       <c r="G29" s="23"/>
@@ -5008,7 +5229,7 @@
       <c r="C30" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D30" s="38"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="36"/>
       <c r="F30" s="24"/>
       <c r="G30" s="23"/>
@@ -5034,7 +5255,7 @@
       <c r="C31" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="38"/>
+      <c r="D31" s="39"/>
       <c r="E31" s="36"/>
       <c r="F31" s="24"/>
       <c r="G31" s="36"/>
@@ -5052,19 +5273,19 @@
       <c r="C32" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="37"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="41"/>
       <c r="F32" s="24"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="40" t="s">
+      <c r="H32" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="41"/>
+      <c r="I32" s="42"/>
       <c r="J32" s="23"/>
-      <c r="K32" s="40" t="s">
+      <c r="K32" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="42"/>
+      <c r="L32" s="38"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="23"/>
@@ -5074,8 +5295,8 @@
       <c r="C33" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="37"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="41"/>
       <c r="F33" s="24"/>
       <c r="G33" s="23"/>
       <c r="H33" s="3" t="s">
@@ -5100,8 +5321,8 @@
       <c r="C34" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="37"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="41"/>
       <c r="F34" s="24"/>
       <c r="G34" s="23"/>
       <c r="H34" s="9" t="s">
@@ -5126,8 +5347,8 @@
       <c r="C35" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="37"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="41"/>
       <c r="F35" s="24"/>
       <c r="G35" s="23"/>
       <c r="H35" s="9" t="s">
@@ -5152,8 +5373,8 @@
       <c r="C36" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="37"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="41"/>
       <c r="F36" s="24"/>
       <c r="G36" s="23"/>
       <c r="H36" s="9" t="s">
@@ -5178,8 +5399,8 @@
       <c r="C37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="37"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="41"/>
       <c r="F37" s="24"/>
       <c r="G37" s="23"/>
       <c r="H37" s="9" t="s">
@@ -5200,8 +5421,8 @@
       <c r="A38" s="36"/>
       <c r="B38" s="36"/>
       <c r="C38" s="24"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
       <c r="F38" s="24"/>
       <c r="G38" s="23"/>
       <c r="H38" s="9" t="s">
@@ -5222,8 +5443,8 @@
       <c r="A39" s="36"/>
       <c r="B39" s="36"/>
       <c r="C39" s="24"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
       <c r="F39" s="24"/>
       <c r="G39" s="36"/>
       <c r="H39" s="36"/>
@@ -5236,8 +5457,8 @@
       <c r="A40" s="36"/>
       <c r="B40" s="36"/>
       <c r="C40" s="24"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41"/>
       <c r="F40" s="24"/>
       <c r="G40" s="36"/>
       <c r="H40" s="36"/>
@@ -5250,8 +5471,8 @@
       <c r="A41" s="36"/>
       <c r="B41" s="36"/>
       <c r="C41" s="24"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
       <c r="F41" s="24"/>
       <c r="G41" s="36"/>
       <c r="H41" s="36"/>
@@ -5262,46 +5483,6 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="G41:H41"/>
@@ -5314,6 +5495,46 @@
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="J40:K40"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6160,128 +6381,617 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="K19:L19"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="E22:F22"/>
   </mergeCells>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="34" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9">
-    <cfRule type="duplicateValues" dxfId="33" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10">
-    <cfRule type="duplicateValues" dxfId="32" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:B15">
-    <cfRule type="duplicateValues" dxfId="31" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26 B20 E18:E19">
-    <cfRule type="duplicateValues" dxfId="30" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27 B12">
-    <cfRule type="duplicateValues" dxfId="29" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31 B24 B13">
-    <cfRule type="duplicateValues" dxfId="28" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="25" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="23" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E20 E15">
-    <cfRule type="duplicateValues" dxfId="20" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27">
-    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="18" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="15" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H26:H27">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H31">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39">
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="6" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:K27">
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31">
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K39">
-    <cfRule type="duplicateValues" dxfId="2" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40">
-    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11 B28">
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="35"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D425E785-15AF-4306-88DC-40102EAE1C35}">
+  <dimension ref="B2:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="3.3984375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="93.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.3984375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="11.59765625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7">
+      <c r="B2" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="33"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="33"/>
+    </row>
+    <row r="3" spans="2:7" ht="14.4">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="27.6">
+      <c r="B13" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="27.6">
+      <c r="B14" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="27.6">
+      <c r="B15" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="E16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="E17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="E18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="14.4">
+      <c r="B19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="27.6">
+      <c r="B20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="31"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="E22" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="33"/>
+    </row>
+    <row r="23" spans="2:6" ht="14.4">
+      <c r="B23" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="33"/>
+      <c r="E23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="14.4">
+      <c r="B24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="D41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="E22:F22"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16 B12">
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27 B21">
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28 B10">
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30 B9">
+    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B25 B11">
+    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="3" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="95.19921875" defaultRowHeight="13.8"/>
@@ -6497,9 +7207,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6704,19 +7417,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6741,9 +7450,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Cronograma de Tareas/Cronograma Septiembre.xlsx
+++ b/Cronograma de Tareas/Cronograma Septiembre.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Alfredo Fuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9974B-1081-44A4-BE8C-281FC6BCBC91}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B80A88E-AEE2-48DA-9709-C777C5C19DEF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-870" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
+    <workbookView xWindow="-28920" yWindow="2475" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{98BEDEB8-80D0-4DE0-A56F-770C1F3168B7}"/>
   </bookViews>
   <sheets>
     <sheet name="Semana 1 - 31 Ago al 6 Sep" sheetId="8" r:id="rId1"/>
     <sheet name="Semana 2 - 7 Sep al 13 Sep" sheetId="9" r:id="rId2"/>
     <sheet name="Semana 3 - 14 al 20 Sep" sheetId="15" r:id="rId3"/>
-    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId4"/>
+    <sheet name="Semana 5 - 28 Sep al 30 Sep" sheetId="16" r:id="rId4"/>
+    <sheet name="Detalle Cronograma" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="107">
   <si>
     <t>Set 1 Mañana</t>
   </si>
@@ -397,6 +398,42 @@
       </rPr>
       <t>lunes y Martes hasta 1:00pm y Miercoles y Jueves hasta las 11:00am, en ausencia de Josue</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Apoyo Revisión GGR negativo casino / deportivo// </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lunes, Martes, Miercoles todo el turno y Jueves en ausencia de Juan Jose</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Apoyo Deltas (Registros, Bonos, Premios Bonos y Bonos Casino)// </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lunes, Martes, Miercoles todo el turno y Jueves en ausencia de Juan Jose</t>
+    </r>
+  </si>
+  <si>
+    <t>Seguimiento Juego Comando - Proveedor Andes Gaming - Cada hora</t>
+  </si>
+  <si>
+    <t>Revisión RiskLive (Usuarios que cruzaron en Pragmatic)</t>
   </si>
 </sst>
 </file>
@@ -613,7 +650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -677,15 +714,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -708,28 +736,230 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="67">
+  <dxfs count="86">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1749,23 +1979,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" s="2" customFormat="1">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="23"/>
-      <c r="H2" s="23" t="s">
+      <c r="F2" s="31"/>
+      <c r="H2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="23"/>
-      <c r="K2" s="23" t="s">
+      <c r="I2" s="31"/>
+      <c r="K2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="23"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B3" s="3" t="s">
@@ -2120,14 +2350,14 @@
       </c>
     </row>
     <row r="17" spans="2:12" s="2" customFormat="1">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="E17" s="23" t="s">
+      <c r="C17" s="31"/>
+      <c r="E17" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="23"/>
+      <c r="F17" s="31"/>
     </row>
     <row r="18" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B18" s="3" t="s">
@@ -2142,14 +2372,14 @@
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="23"/>
-      <c r="K18" s="23" t="s">
+      <c r="I18" s="31"/>
+      <c r="K18" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="23"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" spans="2:12" s="2" customFormat="1" ht="28.95" customHeight="1">
       <c r="B19" s="6" t="s">
@@ -2435,14 +2665,14 @@
       </c>
       <c r="D32"/>
       <c r="F32" s="1"/>
-      <c r="H32" s="24" t="s">
+      <c r="H32" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="25"/>
-      <c r="K32" s="23" t="s">
+      <c r="I32" s="33"/>
+      <c r="K32" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="23"/>
+      <c r="L32" s="31"/>
     </row>
     <row r="33" spans="2:12" s="2" customFormat="1" ht="14.4">
       <c r="B33" s="6" t="s">
@@ -2588,130 +2818,130 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="E17:F17"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="E17:F17"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="66" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="65" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="64" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="63" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B31">
-    <cfRule type="duplicateValues" dxfId="62" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="61" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B34 B9">
-    <cfRule type="duplicateValues" dxfId="60" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35 B29 B11">
-    <cfRule type="duplicateValues" dxfId="59" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="58" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="57" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="56" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="55" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="54" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="53" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="52" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="51" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="duplicateValues" dxfId="50" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="duplicateValues" dxfId="49" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11">
-    <cfRule type="duplicateValues" dxfId="48" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H12">
-    <cfRule type="duplicateValues" dxfId="47" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H13">
-    <cfRule type="duplicateValues" dxfId="46" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="duplicateValues" dxfId="45" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H24">
-    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H25:H26">
-    <cfRule type="duplicateValues" dxfId="43" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H30">
-    <cfRule type="duplicateValues" dxfId="42" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="duplicateValues" dxfId="41" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="40" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="39" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="38" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="37" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="36" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="35" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25">
-    <cfRule type="duplicateValues" dxfId="34" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26">
-    <cfRule type="duplicateValues" dxfId="33" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K27">
-    <cfRule type="duplicateValues" dxfId="32" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="duplicateValues" dxfId="31" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="duplicateValues" dxfId="30" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="duplicateValues" dxfId="29" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="23"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2749,25 +2979,25 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2"/>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="23"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="23"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="23"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="23"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
       <c r="A3" s="2"/>
@@ -3183,10 +3413,10 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2"/>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="23"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="G17" s="2"/>
@@ -3205,20 +3435,20 @@
         <v>5</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="23"/>
+      <c r="F18" s="31"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="23" t="s">
+      <c r="H18" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="23"/>
+      <c r="I18" s="31"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="23" t="s">
+      <c r="K18" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="23"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
       <c r="A19" s="2"/>
@@ -3446,10 +3676,10 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="2"/>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="23"/>
+      <c r="C27" s="31"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="1"/>
@@ -3575,15 +3805,15 @@
       <c r="E32" s="2"/>
       <c r="F32" s="1"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="24" t="s">
+      <c r="H32" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="25"/>
+      <c r="I32" s="33"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="23" t="s">
+      <c r="K32" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="23"/>
+      <c r="L32" s="31"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
       <c r="A33" s="2"/>
@@ -3738,91 +3968,91 @@
     <mergeCell ref="K18:L18"/>
   </mergeCells>
   <conditionalFormatting sqref="B6">
-    <cfRule type="duplicateValues" dxfId="28" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7">
-    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8">
-    <cfRule type="duplicateValues" dxfId="26" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12 B15">
-    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25 B31">
-    <cfRule type="duplicateValues" dxfId="24" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32 B10">
-    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33 B9">
-    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34 B29 B11">
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="duplicateValues" dxfId="17" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E10">
-    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E14">
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23">
-    <cfRule type="duplicateValues" dxfId="12" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H37">
-    <cfRule type="duplicateValues" dxfId="11" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H38">
-    <cfRule type="duplicateValues" dxfId="10" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K12">
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K13">
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K16">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K24">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K25:K26">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37">
-    <cfRule type="duplicateValues" dxfId="1" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3850,62 +4080,62 @@
     <row r="1" spans="1:12">
       <c r="A1" s="34"/>
       <c r="B1" s="34"/>
-      <c r="C1" s="27"/>
+      <c r="C1" s="24"/>
       <c r="D1" s="34"/>
       <c r="E1" s="34"/>
-      <c r="F1" s="27"/>
+      <c r="F1" s="24"/>
       <c r="G1" s="34"/>
       <c r="H1" s="34"/>
-      <c r="I1" s="26"/>
+      <c r="I1" s="23"/>
       <c r="J1" s="34"/>
       <c r="K1" s="34"/>
-      <c r="L1" s="26"/>
+      <c r="L1" s="23"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="26"/>
-      <c r="B2" s="35" t="s">
+      <c r="A2" s="23"/>
+      <c r="B2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="35" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="36"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="35" t="s">
+      <c r="F2" s="40"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="36"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="35" t="s">
+      <c r="I2" s="40"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="36"/>
+      <c r="L2" s="40"/>
     </row>
     <row r="3" spans="1:12" ht="14.4">
-      <c r="A3" s="26"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="27"/>
+      <c r="D3" s="24"/>
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="26"/>
+      <c r="G3" s="23"/>
       <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="26"/>
+      <c r="J3" s="23"/>
       <c r="K3" s="3" t="s">
         <v>4</v>
       </c>
@@ -3914,450 +4144,450 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="14.4">
-      <c r="A4" s="26"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="26"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="23"/>
       <c r="H4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="26"/>
+      <c r="J4" s="23"/>
       <c r="K4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="14.4">
-      <c r="A5" s="26"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="26"/>
+      <c r="D5" s="23"/>
       <c r="E5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="23"/>
       <c r="H5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="26"/>
+      <c r="J5" s="23"/>
       <c r="K5" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="L5" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="14.4">
-      <c r="A6" s="26"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="26"/>
+      <c r="D6" s="23"/>
       <c r="E6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="23"/>
       <c r="H6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J6" s="26"/>
+      <c r="J6" s="23"/>
       <c r="K6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="29" t="s">
+      <c r="L6" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="14.4">
-      <c r="A7" s="26"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="26"/>
+      <c r="D7" s="23"/>
       <c r="E7" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="23"/>
       <c r="H7" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="23"/>
       <c r="K7" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="14.4">
-      <c r="A8" s="26"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="26"/>
+      <c r="D8" s="23"/>
       <c r="E8" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="23"/>
       <c r="H8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="I8" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="26"/>
+      <c r="J8" s="23"/>
       <c r="K8" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="29" t="s">
+      <c r="L8" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="14.4">
-      <c r="A9" s="26"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="26"/>
+      <c r="D9" s="23"/>
       <c r="E9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="26"/>
+      <c r="G9" s="23"/>
       <c r="H9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="23"/>
       <c r="K9" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="L9" s="29" t="s">
+      <c r="L9" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="14.4">
-      <c r="A10" s="26"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="26"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="23"/>
       <c r="H10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="I10" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J10" s="26"/>
+      <c r="J10" s="23"/>
       <c r="K10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="29" t="s">
+      <c r="L10" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="14.4">
-      <c r="A11" s="26"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="26"/>
+      <c r="D11" s="23"/>
       <c r="E11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="23"/>
       <c r="H11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="29" t="s">
+      <c r="I11" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="23"/>
       <c r="K11" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="29" t="s">
+      <c r="L11" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="14.4">
-      <c r="A12" s="26"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="26"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="23"/>
       <c r="H12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="26"/>
+      <c r="J12" s="23"/>
       <c r="K12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="29" t="s">
+      <c r="L12" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="41.4">
-      <c r="A13" s="26"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="27"/>
+      <c r="D13" s="24"/>
       <c r="E13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="23"/>
       <c r="H13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="29" t="s">
+      <c r="I13" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J13" s="26"/>
+      <c r="J13" s="23"/>
       <c r="K13" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="L13" s="29" t="s">
+      <c r="L13" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="41.4">
-      <c r="A14" s="26"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="27"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="23"/>
       <c r="H14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J14" s="26"/>
+      <c r="J14" s="23"/>
       <c r="K14" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L14" s="29" t="s">
+      <c r="L14" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="14.4">
       <c r="A15" s="34"/>
       <c r="B15" s="34"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="26"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="26"/>
+      <c r="G15" s="23"/>
       <c r="H15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="29" t="s">
+      <c r="I15" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="26"/>
+      <c r="J15" s="23"/>
       <c r="K15" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="L15" s="29" t="s">
+      <c r="L15" s="26" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="14.4">
       <c r="A16" s="34"/>
       <c r="B16" s="34"/>
-      <c r="C16" s="27"/>
+      <c r="C16" s="24"/>
       <c r="D16" s="34"/>
       <c r="E16" s="34"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="J16" s="27"/>
+      <c r="J16" s="24"/>
       <c r="K16" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="L16" s="29" t="s">
+      <c r="L16" s="26" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="26"/>
-      <c r="B17" s="35" t="s">
+      <c r="A17" s="23"/>
+      <c r="B17" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="35" t="s">
+      <c r="C17" s="40"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="F17" s="36"/>
+      <c r="F17" s="40"/>
       <c r="G17" s="37"/>
       <c r="H17" s="34"/>
-      <c r="I17" s="26"/>
+      <c r="I17" s="23"/>
       <c r="J17" s="34"/>
       <c r="K17" s="34"/>
-      <c r="L17" s="26"/>
+      <c r="L17" s="23"/>
     </row>
     <row r="18" spans="1:12" ht="14.4">
-      <c r="A18" s="26"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="26"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="26"/>
-      <c r="H18" s="35" t="s">
+      <c r="G18" s="23"/>
+      <c r="H18" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="36"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="35" t="s">
+      <c r="I18" s="40"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="36"/>
+      <c r="L18" s="40"/>
     </row>
     <row r="19" spans="1:12" ht="14.4">
-      <c r="A19" s="26"/>
+      <c r="A19" s="23"/>
       <c r="B19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="26"/>
+      <c r="D19" s="23"/>
       <c r="E19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="26"/>
+      <c r="G19" s="23"/>
       <c r="H19" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J19" s="26"/>
+      <c r="J19" s="23"/>
       <c r="K19" s="3" t="s">
         <v>6</v>
       </c>
@@ -4366,221 +4596,221 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="14.4">
-      <c r="A20" s="26"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="26"/>
+      <c r="D20" s="23"/>
       <c r="E20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="F20" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="26"/>
+      <c r="G20" s="23"/>
       <c r="H20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I20" s="29" t="s">
+      <c r="I20" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J20" s="26"/>
-      <c r="K20" s="30" t="s">
+      <c r="J20" s="23"/>
+      <c r="K20" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="L20" s="28" t="s">
+      <c r="L20" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="26"/>
+      <c r="A21" s="23"/>
       <c r="B21" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="26"/>
+      <c r="D21" s="23"/>
       <c r="E21" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F21" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="26"/>
+      <c r="G21" s="23"/>
       <c r="H21" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="28" t="s">
+      <c r="I21" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="26"/>
-      <c r="K21" s="30" t="s">
+      <c r="J21" s="23"/>
+      <c r="K21" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="L21" s="28" t="s">
+      <c r="L21" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="14.4">
-      <c r="A22" s="26"/>
+      <c r="A22" s="23"/>
       <c r="B22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="26"/>
+      <c r="D22" s="23"/>
       <c r="E22" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G22" s="26"/>
+      <c r="G22" s="23"/>
       <c r="H22" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I22" s="29" t="s">
+      <c r="I22" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="26"/>
-      <c r="K22" s="30" t="s">
+      <c r="J22" s="23"/>
+      <c r="K22" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="L22" s="28" t="s">
+      <c r="L22" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="26"/>
+      <c r="A23" s="23"/>
       <c r="B23" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="25" t="s">
         <v>32</v>
       </c>
       <c r="D23" s="37"/>
       <c r="E23" s="34"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="26"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="23"/>
       <c r="H23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I23" s="28" t="s">
+      <c r="I23" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="26"/>
-      <c r="K23" s="30" t="s">
+      <c r="J23" s="23"/>
+      <c r="K23" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="L23" s="28" t="s">
+      <c r="L23" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="41.4">
-      <c r="A24" s="26"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="25" t="s">
         <v>32</v>
       </c>
       <c r="D24" s="37"/>
       <c r="E24" s="34"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="26"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="23"/>
       <c r="H24" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="29" t="s">
+      <c r="I24" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J24" s="26"/>
-      <c r="K24" s="30" t="s">
+      <c r="J24" s="23"/>
+      <c r="K24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="28" t="s">
+      <c r="L24" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="26"/>
+      <c r="A25" s="23"/>
       <c r="B25" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="25" t="s">
         <v>32</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="34"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="26"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="23"/>
       <c r="H25" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="I25" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J25" s="26"/>
-      <c r="K25" s="30" t="s">
+      <c r="J25" s="23"/>
+      <c r="K25" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="L25" s="28" t="s">
+      <c r="L25" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="14.4">
       <c r="A26" s="34"/>
       <c r="B26" s="34"/>
-      <c r="C26" s="27"/>
+      <c r="C26" s="24"/>
       <c r="D26" s="34"/>
       <c r="E26" s="34"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="26"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="23"/>
       <c r="H26" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="29" t="s">
+      <c r="I26" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="26"/>
-      <c r="K26" s="30" t="s">
+      <c r="J26" s="23"/>
+      <c r="K26" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="L26" s="28" t="s">
+      <c r="L26" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="26"/>
-      <c r="B27" s="35" t="s">
+      <c r="A27" s="23"/>
+      <c r="B27" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="36"/>
+      <c r="C27" s="40"/>
       <c r="D27" s="37"/>
       <c r="E27" s="34"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="26"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="23"/>
       <c r="H27" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="28" t="s">
+      <c r="I27" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J27" s="26"/>
-      <c r="K27" s="30" t="s">
+      <c r="J27" s="23"/>
+      <c r="K27" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="L27" s="28" t="s">
+      <c r="L27" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="14.4">
-      <c r="A28" s="26"/>
+      <c r="A28" s="23"/>
       <c r="B28" s="3" t="s">
         <v>4</v>
       </c>
@@ -4589,133 +4819,133 @@
       </c>
       <c r="D28" s="37"/>
       <c r="E28" s="34"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="26"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="23"/>
       <c r="H28" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="29" t="s">
+      <c r="I28" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J28" s="26"/>
-      <c r="K28" s="30" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="L28" s="28" t="s">
+      <c r="L28" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="26"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="34"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="26"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="23"/>
       <c r="H29" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="I29" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="26"/>
-      <c r="K29" s="30" t="s">
+      <c r="J29" s="23"/>
+      <c r="K29" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="L29" s="28" t="s">
+      <c r="L29" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="27.6">
-      <c r="A30" s="26"/>
-      <c r="B30" s="31" t="s">
+      <c r="A30" s="23"/>
+      <c r="B30" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="37"/>
       <c r="E30" s="34"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="26"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="23"/>
       <c r="H30" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="I30" s="29" t="s">
+      <c r="I30" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="27"/>
+      <c r="J30" s="24"/>
       <c r="K30" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="L30" s="28" t="s">
+      <c r="L30" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="26"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="25" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="37"/>
       <c r="E31" s="34"/>
-      <c r="F31" s="27"/>
+      <c r="F31" s="24"/>
       <c r="G31" s="34"/>
       <c r="H31" s="34"/>
-      <c r="I31" s="26"/>
+      <c r="I31" s="23"/>
       <c r="J31" s="34"/>
       <c r="K31" s="34"/>
-      <c r="L31" s="26"/>
+      <c r="L31" s="23"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="26"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="35" t="s">
+      <c r="D32" s="36"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="I32" s="40"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="35" t="s">
+      <c r="I32" s="39"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="L32" s="36"/>
+      <c r="L32" s="40"/>
     </row>
     <row r="33" spans="1:12" ht="14.4">
-      <c r="A33" s="26"/>
-      <c r="B33" s="32" t="s">
+      <c r="A33" s="23"/>
+      <c r="B33" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="39"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="26"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="23"/>
       <c r="H33" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J33" s="26"/>
+      <c r="J33" s="23"/>
       <c r="K33" s="3" t="s">
         <v>39</v>
       </c>
@@ -4724,175 +4954,215 @@
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="26"/>
-      <c r="B34" s="32" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="39"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="26"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="23"/>
       <c r="H34" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="I34" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="26"/>
+      <c r="J34" s="23"/>
       <c r="K34" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="L34" s="28" t="s">
+      <c r="L34" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="26"/>
+      <c r="A35" s="23"/>
       <c r="B35" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="39"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="26"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="23"/>
       <c r="H35" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I35" s="28" t="s">
+      <c r="I35" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J35" s="26"/>
+      <c r="J35" s="23"/>
       <c r="K35" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="L35" s="28" t="s">
+      <c r="L35" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="26"/>
-      <c r="B36" s="33" t="s">
+      <c r="A36" s="23"/>
+      <c r="B36" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="39"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="26"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="23"/>
       <c r="H36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="I36" s="28" t="s">
+      <c r="I36" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J36" s="26"/>
+      <c r="J36" s="23"/>
       <c r="K36" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L36" s="28" t="s">
+      <c r="L36" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="26"/>
+      <c r="A37" s="23"/>
       <c r="B37" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D37" s="39"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="26"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="23"/>
       <c r="H37" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I37" s="28" t="s">
+      <c r="I37" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J37" s="26"/>
+      <c r="J37" s="23"/>
       <c r="K37" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L37" s="28" t="s">
+      <c r="L37" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="34"/>
       <c r="B38" s="34"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="26"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="23"/>
       <c r="H38" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I38" s="28" t="s">
+      <c r="I38" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J38" s="26"/>
+      <c r="J38" s="23"/>
       <c r="K38" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L38" s="28" t="s">
+      <c r="L38" s="25" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="34"/>
       <c r="B39" s="34"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="27"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="24"/>
       <c r="G39" s="34"/>
       <c r="H39" s="34"/>
-      <c r="I39" s="26"/>
+      <c r="I39" s="23"/>
       <c r="J39" s="34"/>
       <c r="K39" s="34"/>
-      <c r="L39" s="26"/>
+      <c r="L39" s="23"/>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="34"/>
       <c r="B40" s="34"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="27"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="24"/>
       <c r="G40" s="34"/>
       <c r="H40" s="34"/>
-      <c r="I40" s="26"/>
+      <c r="I40" s="23"/>
       <c r="J40" s="34"/>
       <c r="K40" s="34"/>
-      <c r="L40" s="26"/>
+      <c r="L40" s="23"/>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="34"/>
       <c r="B41" s="34"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="27"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="24"/>
       <c r="G41" s="34"/>
       <c r="H41" s="34"/>
-      <c r="I41" s="26"/>
+      <c r="I41" s="23"/>
       <c r="J41" s="34"/>
       <c r="K41" s="34"/>
-      <c r="L41" s="26"/>
+      <c r="L41" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="G41:H41"/>
@@ -4905,52 +5175,501 @@
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="G40:H40"/>
     <mergeCell ref="J40:K40"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{401AAAB1-2BEC-4C38-AB17-54450F407A2A}">
+  <dimension ref="B2:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="3.3984375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="93.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="52.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.09765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.3984375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="11.59765625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7">
+      <c r="B2" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="31"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="31"/>
+    </row>
+    <row r="3" spans="2:7" ht="14.4">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7">
+      <c r="B11" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="27.6">
+      <c r="B13" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1"/>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="27.6">
+      <c r="B14" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="27.6">
+      <c r="B15" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="E16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="E17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="31"/>
+      <c r="E18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="14.4">
+      <c r="B19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="27.6">
+      <c r="B20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="41"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="E22" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" s="31"/>
+    </row>
+    <row r="23" spans="2:6" ht="14.4">
+      <c r="B23" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="31"/>
+      <c r="E23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="14.4">
+      <c r="B24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32"/>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="D34"/>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="D35"/>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="D36"/>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="D37"/>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="D38"/>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="D39"/>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="D40"/>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="D41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:C23"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6">
+    <cfRule type="duplicateValues" dxfId="18" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7">
+    <cfRule type="duplicateValues" dxfId="17" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8">
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16 B12">
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27 B21">
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B28 B10">
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30 B9">
+    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31 B25 B11">
+    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="duplicateValues" dxfId="3" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09747FE2-332F-458B-9A08-92605154E49F}">
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="95.19921875" defaultRowHeight="13.8"/>
@@ -5166,6 +5885,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003DF699C9B971E44AADE72149239363A2" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bd28a159404b63a0ef222e938afe2db3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ef2aad6-6696-4ad1-83da-256baa9d6106" xmlns:ns3="fc5c7554-ce1a-493c-be4c-f5f61635795a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b25b72c149c8f1dd75cad995c7ef7c98" ns2:_="" ns3:_="">
     <xsd:import namespace="3ef2aad6-6696-4ad1-83da-256baa9d6106"/>
@@ -5366,22 +6100,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91E332D-EB99-45DB-9A94-403345151F72}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5398,21 +6134,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FC126E-4B92-445E-9AC5-FE8E280CF6D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6C1C216-E346-4FB0-8480-21EDFFA88808}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>